--- a/docs/DBS4_Corrections_by_Situation_20260921-dbcd48b8.xlsx
+++ b/docs/DBS4_Corrections_by_Situation_20260921-dbcd48b8.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ranking campaigns" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Other campaign types" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B4 keyword diagnosis" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B6 keyword diagnosis" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Syntax groups" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ranking campaigns'!$A$1:$Q$214</definedName>
@@ -16351,4 +16354,6972 @@
   <autoFilter ref="A1:H52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="21" max="21"/>
+    <col width="80" customWidth="1" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Syntax</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Plan clicks/wk</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Weekly SV</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Clicks 30d</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>TOS clicks 30d</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>TOS clicks/day pre-deal</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>TOS clicks/day deal</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>TOS share</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>TOS CTR</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>CTR bar</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>TOS CVR</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>CVR bar</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>TOS impr. share</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Eff. TOS bid</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Organic</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Sponsored</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Rank 24 Jun</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Rank 14 Sep</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Rank 22 Sep</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>bamboo sheets</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bamboo</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>490</v>
+      </c>
+      <c r="D2" t="n">
+        <v>47605</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F2" t="n">
+        <v>934</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>71</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="L2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="M2" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="O2" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="P2" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R2" t="n">
+        <v>33</v>
+      </c>
+      <c r="S2" t="n">
+        <v>32</v>
+      </c>
+      <c r="T2" t="n">
+        <v>41</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>bamboo sheets queen size</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bamboo|Queen</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>248</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10342</v>
+      </c>
+      <c r="E3" t="n">
+        <v>187</v>
+      </c>
+      <c r="F3" t="n">
+        <v>95</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>51</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="L3" t="n">
+        <v>27.16</v>
+      </c>
+      <c r="M3" t="n">
+        <v>13.26</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="O3" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="P3" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>17</v>
+      </c>
+      <c r="R3" t="n">
+        <v>25</v>
+      </c>
+      <c r="S3" t="n">
+        <v>36</v>
+      </c>
+      <c r="T3" t="n">
+        <v>47</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>bamboo sheets king size</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bamboo|King</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>298</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6945</v>
+      </c>
+      <c r="E4" t="n">
+        <v>199</v>
+      </c>
+      <c r="F4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I4" t="n">
+        <v>34</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="L4" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="M4" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="O4" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="P4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>19</v>
+      </c>
+      <c r="R4" t="n">
+        <v>35</v>
+      </c>
+      <c r="S4" t="n">
+        <v>28</v>
+      </c>
+      <c r="T4" t="n">
+        <v>25</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bamboo cooling sheets</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bamboo|Cooling</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>132</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3233</v>
+      </c>
+      <c r="E5" t="n">
+        <v>142</v>
+      </c>
+      <c r="F5" t="n">
+        <v>53</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I5" t="n">
+        <v>37</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="L5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P5" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>12</v>
+      </c>
+      <c r="R5" t="n">
+        <v>28</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="n">
+        <v>31</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cooling sheets</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cooling</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>232</v>
+      </c>
+      <c r="D6" t="n">
+        <v>23852</v>
+      </c>
+      <c r="E6" t="n">
+        <v>341</v>
+      </c>
+      <c r="F6" t="n">
+        <v>98</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>29</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="P6" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>12</v>
+      </c>
+      <c r="R6" t="n">
+        <v>55</v>
+      </c>
+      <c r="S6" t="n">
+        <v>55</v>
+      </c>
+      <c r="T6" t="n">
+        <v>56</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>BOTH — short of traffic and under target</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Fix the offer first, then buy traffic: a small TOS probe (+10%) only while the CTR/CVR fix is made.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>bamboo sheets queen</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bamboo|Queen</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>858</v>
+      </c>
+      <c r="E7" t="n">
+        <v>218</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="L7" t="n">
+        <v>43.34</v>
+      </c>
+      <c r="M7" t="n">
+        <v>13.26</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P7" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>29</v>
+      </c>
+      <c r="S7" t="n">
+        <v>58</v>
+      </c>
+      <c r="T7" t="n">
+        <v>71</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>bamboo sheets king</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bamboo|King</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>70</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2680</v>
+      </c>
+      <c r="E8" t="n">
+        <v>33</v>
+      </c>
+      <c r="F8" t="n">
+        <v>21</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>63</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="L8" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="M8" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="O8" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="P8" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>15</v>
+      </c>
+      <c r="R8" t="n">
+        <v>21</v>
+      </c>
+      <c r="S8" t="n">
+        <v>30</v>
+      </c>
+      <c r="T8" t="n">
+        <v>28</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>king cooling sheets</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cooling|King</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>19</v>
+      </c>
+      <c r="D9" t="n">
+        <v>954</v>
+      </c>
+      <c r="E9" t="n">
+        <v>18</v>
+      </c>
+      <c r="F9" t="n">
+        <v>14</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>77</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="L9" t="n">
+        <v>31.02</v>
+      </c>
+      <c r="M9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="O9" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="P9" t="n">
+        <v>48</v>
+      </c>
+      <c r="R9" t="n">
+        <v>55</v>
+      </c>
+      <c r="S9" t="n">
+        <v>56</v>
+      </c>
+      <c r="T9" t="n">
+        <v>44</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>bamboo king sheets</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bamboo|King</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>150</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1148</v>
+      </c>
+      <c r="E10" t="n">
+        <v>33</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>30</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="L10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M10" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="P10" t="n">
+        <v>32</v>
+      </c>
+      <c r="R10" t="n">
+        <v>24</v>
+      </c>
+      <c r="S10" t="n">
+        <v>23</v>
+      </c>
+      <c r="T10" t="n">
+        <v>43</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>bamboo viscose sheets</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bamboo</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>116</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1148</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>26</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="P11" t="n">
+        <v>48</v>
+      </c>
+      <c r="R11" t="n">
+        <v>37</v>
+      </c>
+      <c r="S11" t="n">
+        <v>41</v>
+      </c>
+      <c r="T11" t="n">
+        <v>45</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>bamboo sheets full size</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Bamboo|Full</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>651</v>
+      </c>
+      <c r="E12" t="n">
+        <v>101</v>
+      </c>
+      <c r="F12" t="n">
+        <v>36</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>35</v>
+      </c>
+      <c r="J12" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="L12" t="n">
+        <v>20.93</v>
+      </c>
+      <c r="M12" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="P12" t="n">
+        <v>47</v>
+      </c>
+      <c r="R12" t="n">
+        <v>30</v>
+      </c>
+      <c r="S12" t="n">
+        <v>36</v>
+      </c>
+      <c r="T12" t="n">
+        <v>38</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>ON TRACK</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Meets the CTR/CVR bars and wins TOS: scale while rank moves; if rank stalls, the gap is volume vs rivals — raise by the rank-gap step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cooling sheets queen</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Cooling|Queen</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>81</v>
+      </c>
+      <c r="D13" t="n">
+        <v>10426</v>
+      </c>
+      <c r="E13" t="n">
+        <v>243</v>
+      </c>
+      <c r="F13" t="n">
+        <v>51</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I13" t="n">
+        <v>21</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="L13" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="M13" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="P13" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>12</v>
+      </c>
+      <c r="R13" t="n">
+        <v>120</v>
+      </c>
+      <c r="S13" t="n">
+        <v>120</v>
+      </c>
+      <c r="T13" t="n">
+        <v>45</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>king bamboo sheets</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bamboo|King</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>63</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1355</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>60</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="L14" t="n">
+        <v>27.92</v>
+      </c>
+      <c r="M14" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="O14" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="P14" t="n">
+        <v>38</v>
+      </c>
+      <c r="R14" t="n">
+        <v>24</v>
+      </c>
+      <c r="S14" t="n">
+        <v>30</v>
+      </c>
+      <c r="T14" t="n">
+        <v>25</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>bamboo sheets twin</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Bamboo|Twin</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>9</v>
+      </c>
+      <c r="D15" t="n">
+        <v>714</v>
+      </c>
+      <c r="E15" t="n">
+        <v>14</v>
+      </c>
+      <c r="F15" t="n">
+        <v>9</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>65</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="L15" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="M15" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="P15" t="n">
+        <v>22</v>
+      </c>
+      <c r="R15" t="n">
+        <v>17</v>
+      </c>
+      <c r="S15" t="n">
+        <v>21</v>
+      </c>
+      <c r="T15" t="n">
+        <v>50</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>queen bamboo sheet set</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Bamboo|Queen</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1397</v>
+      </c>
+      <c r="E16" t="n">
+        <v>21</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="L16" t="n">
+        <v>53.17</v>
+      </c>
+      <c r="M16" t="n">
+        <v>13.26</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P16" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>12</v>
+      </c>
+      <c r="R16" t="n">
+        <v>31</v>
+      </c>
+      <c r="S16" t="n">
+        <v>27</v>
+      </c>
+      <c r="T16" t="n">
+        <v>37</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>bamboo sheets deep pocket</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Bamboo</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>141</v>
+      </c>
+      <c r="E17" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>65</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="L17" t="n">
+        <v>52.55</v>
+      </c>
+      <c r="M17" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="P17" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>17</v>
+      </c>
+      <c r="R17" t="n">
+        <v>36</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="n">
+        <v>26</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>bamboo bed sheets</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Bamboo</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>73</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1564</v>
+      </c>
+      <c r="E18" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>18</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="L18" t="n">
+        <v>61.83</v>
+      </c>
+      <c r="M18" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="P18" t="n">
+        <v>41</v>
+      </c>
+      <c r="R18" t="n">
+        <v>42</v>
+      </c>
+      <c r="S18" t="n">
+        <v>40</v>
+      </c>
+      <c r="T18" t="n">
+        <v>47</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cooling sheet</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Cooling</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>280</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>31</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>112.42</v>
+      </c>
+      <c r="M19" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="P19" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>14</v>
+      </c>
+      <c r="R19" t="n">
+        <v>47</v>
+      </c>
+      <c r="S19" t="n">
+        <v>70</v>
+      </c>
+      <c r="T19" t="n">
+        <v>92</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>king size bamboo sheets set</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Bamboo|King</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>62</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1367</v>
+      </c>
+      <c r="E20" t="n">
+        <v>51</v>
+      </c>
+      <c r="F20" t="n">
+        <v>31</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>62</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="L20" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="M20" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="N20" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="O20" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="P20" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>10</v>
+      </c>
+      <c r="R20" t="n">
+        <v>39</v>
+      </c>
+      <c r="S20" t="n">
+        <v>32</v>
+      </c>
+      <c r="T20" t="n">
+        <v>39</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>bamboo sheets king size deep pocket</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bamboo|King</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>39</v>
+      </c>
+      <c r="D21" t="n">
+        <v>333</v>
+      </c>
+      <c r="E21" t="n">
+        <v>30</v>
+      </c>
+      <c r="F21" t="n">
+        <v>20</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>66</v>
+      </c>
+      <c r="J21" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="L21" t="n">
+        <v>27.92</v>
+      </c>
+      <c r="M21" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="O21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>34</v>
+      </c>
+      <c r="S21" t="n">
+        <v>27</v>
+      </c>
+      <c r="T21" t="n">
+        <v>23</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>bamboo sheets full</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bamboo|Full</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>16</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1588</v>
+      </c>
+      <c r="E22" t="n">
+        <v>42</v>
+      </c>
+      <c r="F22" t="n">
+        <v>12</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I22" t="n">
+        <v>29</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="L22" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="M22" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="P22" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>10</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>twin bamboo sheets set</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Bamboo|Twin</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>75</v>
+      </c>
+      <c r="E23" t="n">
+        <v>72</v>
+      </c>
+      <c r="F23" t="n">
+        <v>11</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I23" t="n">
+        <v>16</v>
+      </c>
+      <c r="J23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="L23" t="n">
+        <v>23.26</v>
+      </c>
+      <c r="M23" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="P23" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>king sheets cooling</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Cooling|King</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>45</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1541</v>
+      </c>
+      <c r="E24" t="n">
+        <v>26</v>
+      </c>
+      <c r="F24" t="n">
+        <v>17</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>65</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="L24" t="n">
+        <v>33.06</v>
+      </c>
+      <c r="M24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O24" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="P24" t="n">
+        <v>26</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>extra deep 20-24 inch pocket king size bamboo sheets</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Bamboo|King</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>175</v>
+      </c>
+      <c r="E25" t="n">
+        <v>46</v>
+      </c>
+      <c r="F25" t="n">
+        <v>9</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>21</v>
+      </c>
+      <c r="J25" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="L25" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="M25" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="P25" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>5</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>purple bamboo sheets</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Bamboo</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>127</v>
+      </c>
+      <c r="E26" t="n">
+        <v>65</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M26" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="P26" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>king size bamboo sheet sets cooling</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Bamboo|Cooling</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>39</v>
+      </c>
+      <c r="F27" t="n">
+        <v>6</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>17</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="L27" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="M27" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>twin cooling sheets</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Cooling|Twin</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>349</v>
+      </c>
+      <c r="E28" t="n">
+        <v>29</v>
+      </c>
+      <c r="F28" t="n">
+        <v>14</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>48</v>
+      </c>
+      <c r="J28" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="L28" t="n">
+        <v>48.13</v>
+      </c>
+      <c r="M28" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="P28" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>king size cooling sheets</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Cooling|King</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>29</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1588</v>
+      </c>
+      <c r="E29" t="n">
+        <v>22</v>
+      </c>
+      <c r="F29" t="n">
+        <v>16</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I29" t="n">
+        <v>75</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="L29" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="M29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O29" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="P29" t="n">
+        <v>45</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>full size bamboo sheets</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Bamboo|Full</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>460</v>
+      </c>
+      <c r="E30" t="n">
+        <v>20</v>
+      </c>
+      <c r="F30" t="n">
+        <v>13</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I30" t="n">
+        <v>65</v>
+      </c>
+      <c r="J30" t="n">
+        <v>12.04</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="L30" t="n">
+        <v>55.83</v>
+      </c>
+      <c r="M30" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="P30" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>16</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>king sheets deep pocket bamboo</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Bamboo|King</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>93</v>
+      </c>
+      <c r="E31" t="n">
+        <v>11</v>
+      </c>
+      <c r="F31" t="n">
+        <v>10</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I31" t="n">
+        <v>93</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M31" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="O31" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="P31" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>cooling sheets king</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Cooling|King</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>50</v>
+      </c>
+      <c r="D32" t="n">
+        <v>886</v>
+      </c>
+      <c r="E32" t="n">
+        <v>27</v>
+      </c>
+      <c r="F32" t="n">
+        <v>11</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I32" t="n">
+        <v>40</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N32" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="O32" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="P32" t="n">
+        <v>44</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>100% bamboo sheets king size</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Bamboo|King</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>40</v>
+      </c>
+      <c r="D33" t="n">
+        <v>260</v>
+      </c>
+      <c r="E33" t="n">
+        <v>28</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>15</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="L33" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="M33" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="P33" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>9</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>full size sheets bamboo</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Bamboo|Full</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>161</v>
+      </c>
+      <c r="E34" t="n">
+        <v>14</v>
+      </c>
+      <c r="F34" t="n">
+        <v>10</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>72</v>
+      </c>
+      <c r="J34" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="M34" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="P34" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>california king bamboo sheet sets</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Bamboo|California King</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>90</v>
+      </c>
+      <c r="E35" t="n">
+        <v>19</v>
+      </c>
+      <c r="F35" t="n">
+        <v>6</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I35" t="n">
+        <v>33</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="M35" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="P35" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>bamboo cooling sheets queen</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Bamboo|Cooling</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>498</v>
+      </c>
+      <c r="E36" t="n">
+        <v>27</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>5</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P36" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="21" max="21"/>
+    <col width="80" customWidth="1" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Syntax</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Plan clicks/wk</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Weekly SV</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Clicks 30d</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>TOS clicks 30d</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>TOS clicks/day pre-deal</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>TOS clicks/day deal</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>TOS share</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>TOS CTR</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>CTR bar</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>TOS CVR</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>CVR bar</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>TOS impr. share</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Eff. TOS bid</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Organic</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Sponsored</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Rank 24 Jun</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Rank 14 Sep</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Rank 22 Sep</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>bamboo sheets</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bamboo</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>47605</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1036</v>
+      </c>
+      <c r="F2" t="n">
+        <v>382</v>
+      </c>
+      <c r="G2" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I2" t="n">
+        <v>37</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="L2" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="M2" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="O2" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>19</v>
+      </c>
+      <c r="R2" t="n">
+        <v>23</v>
+      </c>
+      <c r="S2" t="n">
+        <v>25</v>
+      </c>
+      <c r="T2" t="n">
+        <v>35</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>viscose bamboo sheets</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bamboo</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>642</v>
+      </c>
+      <c r="E3" t="n">
+        <v>169</v>
+      </c>
+      <c r="F3" t="n">
+        <v>57</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>34</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="L3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="M3" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O3" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="P3" t="n">
+        <v>12</v>
+      </c>
+      <c r="R3" t="n">
+        <v>16</v>
+      </c>
+      <c r="S3" t="n">
+        <v>13</v>
+      </c>
+      <c r="T3" t="n">
+        <v>13</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>king size bamboo sheets set</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bamboo|King</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1367</v>
+      </c>
+      <c r="E4" t="n">
+        <v>128</v>
+      </c>
+      <c r="F4" t="n">
+        <v>47</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>37</v>
+      </c>
+      <c r="J4" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="L4" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="M4" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="N4" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="O4" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="P4" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>9</v>
+      </c>
+      <c r="S4" t="n">
+        <v>29</v>
+      </c>
+      <c r="T4" t="n">
+        <v>36</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bamboo sheets queen size</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bamboo|Queen</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10342</v>
+      </c>
+      <c r="E5" t="n">
+        <v>166</v>
+      </c>
+      <c r="F5" t="n">
+        <v>38</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>23</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="L5" t="n">
+        <v>32.84</v>
+      </c>
+      <c r="M5" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="P5" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>28</v>
+      </c>
+      <c r="S5" t="n">
+        <v>32</v>
+      </c>
+      <c r="T5" t="n">
+        <v>32</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>bamboo bed sheets</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bamboo</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1564</v>
+      </c>
+      <c r="E6" t="n">
+        <v>44</v>
+      </c>
+      <c r="F6" t="n">
+        <v>35</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>78</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="L6" t="n">
+        <v>16.88</v>
+      </c>
+      <c r="M6" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="O6" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="P6" t="n">
+        <v>40</v>
+      </c>
+      <c r="R6" t="n">
+        <v>31</v>
+      </c>
+      <c r="S6" t="n">
+        <v>31</v>
+      </c>
+      <c r="T6" t="n">
+        <v>27</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>bamboo sheets with corner straps</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bamboo</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>115</v>
+      </c>
+      <c r="E7" t="n">
+        <v>75</v>
+      </c>
+      <c r="F7" t="n">
+        <v>29</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I7" t="n">
+        <v>39</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="L7" t="n">
+        <v>21.67</v>
+      </c>
+      <c r="M7" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="N7" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="O7" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="P7" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>23</v>
+      </c>
+      <c r="S7" t="n">
+        <v>13</v>
+      </c>
+      <c r="T7" t="n">
+        <v>14</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>ON TRACK</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Meets the CTR/CVR bars and wins TOS: scale while rank moves; if rank stalls, the gap is volume vs rivals — raise by the rank-gap step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>queen sheet set bamboo</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bamboo|Queen</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>366</v>
+      </c>
+      <c r="E8" t="n">
+        <v>97</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M8" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="P8" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>18</v>
+      </c>
+      <c r="S8" t="n">
+        <v>35</v>
+      </c>
+      <c r="T8" t="n">
+        <v>44</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>bamboo king sheets</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bamboo|King</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1148</v>
+      </c>
+      <c r="E9" t="n">
+        <v>33</v>
+      </c>
+      <c r="F9" t="n">
+        <v>30</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>90</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M9" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="N9" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="O9" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="P9" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>17</v>
+      </c>
+      <c r="R9" t="n">
+        <v>16</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="n">
+        <v>18</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>bamboo sheets full</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bamboo|Full</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1588</v>
+      </c>
+      <c r="E10" t="n">
+        <v>51</v>
+      </c>
+      <c r="F10" t="n">
+        <v>35</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>69</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="M10" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="O10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>58</v>
+      </c>
+      <c r="S10" t="n">
+        <v>13</v>
+      </c>
+      <c r="T10" t="n">
+        <v>11</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>king bamboo sheets</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bamboo|King</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1355</v>
+      </c>
+      <c r="E11" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" t="n">
+        <v>12</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>21</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M11" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="P11" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>9</v>
+      </c>
+      <c r="R11" t="n">
+        <v>23</v>
+      </c>
+      <c r="S11" t="n">
+        <v>31</v>
+      </c>
+      <c r="T11" t="n">
+        <v>40</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>BOTH — short of traffic and under target</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Fix the offer first, then buy traffic: a small TOS probe (+10%) only while the CTR/CVR fix is made.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>bamboo sheets king size</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Bamboo|King</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>6945</v>
+      </c>
+      <c r="E12" t="n">
+        <v>54</v>
+      </c>
+      <c r="F12" t="n">
+        <v>17</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>32</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M12" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P12" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>19</v>
+      </c>
+      <c r="R12" t="n">
+        <v>15</v>
+      </c>
+      <c r="S12" t="n">
+        <v>36</v>
+      </c>
+      <c r="T12" t="n">
+        <v>38</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>red bamboo sheets</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>53</v>
+      </c>
+      <c r="F13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>45</v>
+      </c>
+      <c r="J13" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="L13" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="N13" t="n">
+        <v>26.58</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>black bamboo sheets</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bamboo</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>463</v>
+      </c>
+      <c r="E14" t="n">
+        <v>30</v>
+      </c>
+      <c r="F14" t="n">
+        <v>19</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>62</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M14" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="P14" t="n">
+        <v>13</v>
+      </c>
+      <c r="R14" t="n">
+        <v>18</v>
+      </c>
+      <c r="S14" t="n">
+        <v>21</v>
+      </c>
+      <c r="T14" t="n">
+        <v>17</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>bamboo cooling sheets</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Bamboo|Cooling</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3233</v>
+      </c>
+      <c r="E15" t="n">
+        <v>44</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>7</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="L15" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="M15" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="P15" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>17</v>
+      </c>
+      <c r="R15" t="n">
+        <v>30</v>
+      </c>
+      <c r="S15" t="n">
+        <v>35</v>
+      </c>
+      <c r="T15" t="n">
+        <v>27</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>bamboo sheet set</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Bamboo</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>545</v>
+      </c>
+      <c r="E16" t="n">
+        <v>31</v>
+      </c>
+      <c r="F16" t="n">
+        <v>16</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>51</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M16" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="O16" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="P16" t="n">
+        <v>58</v>
+      </c>
+      <c r="R16" t="n">
+        <v>22</v>
+      </c>
+      <c r="S16" t="n">
+        <v>48</v>
+      </c>
+      <c r="T16" t="n">
+        <v>38</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>burgundy sheets queen</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>352</v>
+      </c>
+      <c r="E17" t="n">
+        <v>27</v>
+      </c>
+      <c r="F17" t="n">
+        <v>9</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I17" t="n">
+        <v>33</v>
+      </c>
+      <c r="P17" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>47</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>full bamboo sheets</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Bamboo|Full</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>200</v>
+      </c>
+      <c r="E18" t="n">
+        <v>22</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I18" t="n">
+        <v>45</v>
+      </c>
+      <c r="J18" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="M18" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="N18" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="O18" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="P18" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>15</v>
+      </c>
+      <c r="S18" t="n">
+        <v>12</v>
+      </c>
+      <c r="T18" t="n">
+        <v>13</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>bamboo twin sheets</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Bamboo|Twin</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>417</v>
+      </c>
+      <c r="E19" t="n">
+        <v>20</v>
+      </c>
+      <c r="F19" t="n">
+        <v>7</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>35</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="M19" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="P19" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>18</v>
+      </c>
+      <c r="R19" t="n">
+        <v>13</v>
+      </c>
+      <c r="S19" t="n">
+        <v>28</v>
+      </c>
+      <c r="T19" t="n">
+        <v>25</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>bamboo full size bed sheets</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Bamboo|Full</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>197</v>
+      </c>
+      <c r="E20" t="n">
+        <v>14</v>
+      </c>
+      <c r="F20" t="n">
+        <v>13</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I20" t="n">
+        <v>89</v>
+      </c>
+      <c r="J20" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="L20" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="M20" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="P20" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>20</v>
+      </c>
+      <c r="R20" t="n">
+        <v>36</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="n">
+        <v>26</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>bamboo sheets queen</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bamboo|Queen</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>858</v>
+      </c>
+      <c r="E21" t="n">
+        <v>37</v>
+      </c>
+      <c r="F21" t="n">
+        <v>7</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>20</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M21" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="P21" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>8</v>
+      </c>
+      <c r="R21" t="n">
+        <v>18</v>
+      </c>
+      <c r="S21" t="n">
+        <v>39</v>
+      </c>
+      <c r="T21" t="n">
+        <v>55</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sheets queen size bed set</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>23315</v>
+      </c>
+      <c r="E22" t="n">
+        <v>41</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="P22" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>17</v>
+      </c>
+      <c r="R22" t="n">
+        <v>48</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cooling bed sheets</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Cooling</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5185</v>
+      </c>
+      <c r="E23" t="n">
+        <v>20</v>
+      </c>
+      <c r="F23" t="n">
+        <v>12</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I23" t="n">
+        <v>59</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="P23" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>22</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>twin sheets bamboo</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Bamboo|Twin</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>203</v>
+      </c>
+      <c r="E24" t="n">
+        <v>21</v>
+      </c>
+      <c r="F24" t="n">
+        <v>8</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>38</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="M24" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="P24" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>bamboo sheets pink</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>29</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>11</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>full size bamboo sheets</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Bamboo|Full</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>460</v>
+      </c>
+      <c r="E26" t="n">
+        <v>18</v>
+      </c>
+      <c r="F26" t="n">
+        <v>8</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>46</v>
+      </c>
+      <c r="J26" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="M26" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O26" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="P26" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>15</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>bamboo viscose sheets queen size</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Bamboo|Queen</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>124</v>
+      </c>
+      <c r="E27" t="n">
+        <v>15</v>
+      </c>
+      <c r="F27" t="n">
+        <v>9</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>59</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M27" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="P27" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>bamboo sheets twin</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Bamboo|Twin</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>714</v>
+      </c>
+      <c r="E28" t="n">
+        <v>26</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>9</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="M28" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="P28" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>24</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>100% bamboo sheets king size</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Bamboo|King</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>260</v>
+      </c>
+      <c r="E29" t="n">
+        <v>18</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>24</v>
+      </c>
+      <c r="J29" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M29" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="P29" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>15</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>king bamboo sheets deep pocket</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Bamboo|King</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>355</v>
+      </c>
+      <c r="E30" t="n">
+        <v>13</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>43</v>
+      </c>
+      <c r="J30" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M30" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="P30" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>bamboo sheet sets</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Bamboo</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>121</v>
+      </c>
+      <c r="E31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>56</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M31" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="N31" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="O31" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="P31" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>12</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>queen bamboo sheet set</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Bamboo|Queen</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1397</v>
+      </c>
+      <c r="E32" t="n">
+        <v>15</v>
+      </c>
+      <c r="F32" t="n">
+        <v>7</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>48</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M32" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="O32" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="P32" t="n">
+        <v>21</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>queen size sheets bamboo</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Bamboo|Queen</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>107</v>
+      </c>
+      <c r="E33" t="n">
+        <v>7</v>
+      </c>
+      <c r="F33" t="n">
+        <v>7</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I33" t="n">
+        <v>100</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M33" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="P33" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>king bed bamboo sheets</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Bamboo|King</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>319</v>
+      </c>
+      <c r="E34" t="n">
+        <v>11</v>
+      </c>
+      <c r="F34" t="n">
+        <v>5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>49</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M34" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="P34" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>27</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>cooling bed sheets king</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Cooling|King</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>492</v>
+      </c>
+      <c r="E35" t="n">
+        <v>8</v>
+      </c>
+      <c r="F35" t="n">
+        <v>7</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I35" t="n">
+        <v>90</v>
+      </c>
+      <c r="J35" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="M35" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="P35" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>11</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>bamboo sheets california king</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Bamboo|California King</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>420</v>
+      </c>
+      <c r="E36" t="n">
+        <v>17</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>5</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="M36" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O36" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="P36" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>6</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>queen sheets set bamboo</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>18</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O37" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>bamboo sheets king</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Bamboo|King</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>2680</v>
+      </c>
+      <c r="E38" t="n">
+        <v>11</v>
+      </c>
+      <c r="F38" t="n">
+        <v>8</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>74</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M38" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="O38" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P38" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>19</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>bamboo king size sheets</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Bamboo|King</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>132</v>
+      </c>
+      <c r="E39" t="n">
+        <v>8</v>
+      </c>
+      <c r="F39" t="n">
+        <v>5</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I39" t="n">
+        <v>67</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M39" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="P39" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>17</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>extra deep 20-24 inch pocket king size bamboo sheets</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Bamboo|King</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>175</v>
+      </c>
+      <c r="E40" t="n">
+        <v>8</v>
+      </c>
+      <c r="F40" t="n">
+        <v>7</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I40" t="n">
+        <v>91</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="P40" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>king sheets bamboo</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Bamboo|King</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>766</v>
+      </c>
+      <c r="E41" t="n">
+        <v>10</v>
+      </c>
+      <c r="F41" t="n">
+        <v>5</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>46</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M41" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="O41" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="P41" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>25</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Spend 30d</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TOS clicks</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>TOS share</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>TOS CTR</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>CTR bar</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>TOS CVR</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>CVR bar</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>TOS impr. share</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>TOS CPC</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Rank 24 Jun</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Rank 15 Aug</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Rank 14 Sep</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Rank 22 Sep</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bamboo</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>17929.38</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5046</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1006</v>
+      </c>
+      <c r="F2" t="n">
+        <v>65</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="I2" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="J2" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="L2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M2" t="n">
+        <v>31</v>
+      </c>
+      <c r="N2" t="n">
+        <v>33</v>
+      </c>
+      <c r="O2" t="n">
+        <v>35</v>
+      </c>
+      <c r="P2" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Cooling</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5070.609999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1577</v>
+      </c>
+      <c r="E3" t="n">
+        <v>110</v>
+      </c>
+      <c r="F3" t="n">
+        <v>29</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="J3" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M3" t="n">
+        <v>81</v>
+      </c>
+      <c r="N3" t="n">
+        <v>67</v>
+      </c>
+      <c r="O3" t="n">
+        <v>65</v>
+      </c>
+      <c r="P3" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>PERFORMANCE GAP — shown, but CVR under target</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bamboo|King</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2724.349999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>645</v>
+      </c>
+      <c r="E4" t="n">
+        <v>251</v>
+      </c>
+      <c r="F4" t="n">
+        <v>44</v>
+      </c>
+      <c r="G4" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I4" t="n">
+        <v>18.09</v>
+      </c>
+      <c r="J4" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="L4" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="M4" t="n">
+        <v>34</v>
+      </c>
+      <c r="N4" t="n">
+        <v>29</v>
+      </c>
+      <c r="O4" t="n">
+        <v>30</v>
+      </c>
+      <c r="P4" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bamboo|Queen</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2223.01</v>
+      </c>
+      <c r="D5" t="n">
+        <v>568</v>
+      </c>
+      <c r="E5" t="n">
+        <v>125</v>
+      </c>
+      <c r="F5" t="n">
+        <v>24</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I5" t="n">
+        <v>23.96</v>
+      </c>
+      <c r="J5" t="n">
+        <v>13.26</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="M5" t="n">
+        <v>32</v>
+      </c>
+      <c r="N5" t="n">
+        <v>43</v>
+      </c>
+      <c r="O5" t="n">
+        <v>42</v>
+      </c>
+      <c r="P5" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Size: King</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1741.91</v>
+      </c>
+      <c r="D6" t="n">
+        <v>679</v>
+      </c>
+      <c r="E6" t="n">
+        <v>628</v>
+      </c>
+      <c r="F6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G6" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="J6" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ON TRACK</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cooling|Queen</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1091.08</v>
+      </c>
+      <c r="D7" t="n">
+        <v>302</v>
+      </c>
+      <c r="E7" t="n">
+        <v>56</v>
+      </c>
+      <c r="F7" t="n">
+        <v>21</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="I7" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="J7" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>111</v>
+      </c>
+      <c r="N7" t="n">
+        <v>91</v>
+      </c>
+      <c r="O7" t="n">
+        <v>79</v>
+      </c>
+      <c r="P7" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>ON TRACK</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bamboo|Cooling</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>990.25</v>
+      </c>
+      <c r="D8" t="n">
+        <v>282</v>
+      </c>
+      <c r="E8" t="n">
+        <v>90</v>
+      </c>
+      <c r="F8" t="n">
+        <v>33</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="I8" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="J8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>24.32</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="M8" t="n">
+        <v>36</v>
+      </c>
+      <c r="N8" t="n">
+        <v>31</v>
+      </c>
+      <c r="O8" t="n">
+        <v>36</v>
+      </c>
+      <c r="P8" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>ON TRACK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cooling|King</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>898.5000000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>221</v>
+      </c>
+      <c r="E9" t="n">
+        <v>90</v>
+      </c>
+      <c r="F9" t="n">
+        <v>61</v>
+      </c>
+      <c r="G9" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="I9" t="n">
+        <v>17.61</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="M9" t="n">
+        <v>71</v>
+      </c>
+      <c r="N9" t="n">
+        <v>60</v>
+      </c>
+      <c r="O9" t="n">
+        <v>67</v>
+      </c>
+      <c r="P9" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bamboo|Full</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>737.4599999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>239</v>
+      </c>
+      <c r="E10" t="n">
+        <v>86</v>
+      </c>
+      <c r="F10" t="n">
+        <v>46</v>
+      </c>
+      <c r="G10" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I10" t="n">
+        <v>30.38</v>
+      </c>
+      <c r="J10" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="M10" t="n">
+        <v>22</v>
+      </c>
+      <c r="N10" t="n">
+        <v>33</v>
+      </c>
+      <c r="O10" t="n">
+        <v>61</v>
+      </c>
+      <c r="P10" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>ON TRACK</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Size: Queen</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>708.2000000000002</v>
+      </c>
+      <c r="D11" t="n">
+        <v>325</v>
+      </c>
+      <c r="E11" t="n">
+        <v>258</v>
+      </c>
+      <c r="F11" t="n">
+        <v>22</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I11" t="n">
+        <v>19.19</v>
+      </c>
+      <c r="J11" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>ON TRACK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Size: Full</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>405.3699999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>228</v>
+      </c>
+      <c r="E12" t="n">
+        <v>155</v>
+      </c>
+      <c r="F12" t="n">
+        <v>34</v>
+      </c>
+      <c r="G12" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="I12" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>ON TRACK</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Bamboo|Twin</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>288.58</v>
+      </c>
+      <c r="D13" t="n">
+        <v>133</v>
+      </c>
+      <c r="E13" t="n">
+        <v>28</v>
+      </c>
+      <c r="F13" t="n">
+        <v>24</v>
+      </c>
+      <c r="G13" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="I13" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="M13" t="n">
+        <v>11</v>
+      </c>
+      <c r="N13" t="n">
+        <v>23</v>
+      </c>
+      <c r="O13" t="n">
+        <v>21</v>
+      </c>
+      <c r="P13" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bamboo|California King</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>277.3200000000001</v>
+      </c>
+      <c r="D14" t="n">
+        <v>76</v>
+      </c>
+      <c r="E14" t="n">
+        <v>30</v>
+      </c>
+      <c r="F14" t="n">
+        <v>40</v>
+      </c>
+      <c r="G14" t="n">
+        <v>27.34</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="I14" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="J14" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="M14" t="n">
+        <v>28</v>
+      </c>
+      <c r="N14" t="n">
+        <v>14</v>
+      </c>
+      <c r="O14" t="n">
+        <v>12</v>
+      </c>
+      <c r="P14" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Size: California King</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>210.2599999999999</v>
+      </c>
+      <c r="D15" t="n">
+        <v>90</v>
+      </c>
+      <c r="E15" t="n">
+        <v>62</v>
+      </c>
+      <c r="F15" t="n">
+        <v>36</v>
+      </c>
+      <c r="G15" t="n">
+        <v>32.46</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I15" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="J15" t="n">
+        <v>16.02</v>
+      </c>
+      <c r="L15" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>BOTH — short of traffic and under target</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Size: Twin</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>152.67</v>
+      </c>
+      <c r="D16" t="n">
+        <v>80</v>
+      </c>
+      <c r="E16" t="n">
+        <v>65</v>
+      </c>
+      <c r="F16" t="n">
+        <v>24</v>
+      </c>
+      <c r="G16" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I16" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="J16" t="n">
+        <v>21.21</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>ON TRACK</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Cooling|Full</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>146.35</v>
+      </c>
+      <c r="D17" t="n">
+        <v>57</v>
+      </c>
+      <c r="E17" t="n">
+        <v>12</v>
+      </c>
+      <c r="F17" t="n">
+        <v>31</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="I17" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="J17" t="n">
+        <v>12.51</v>
+      </c>
+      <c r="L17" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="M17" t="n">
+        <v>69</v>
+      </c>
+      <c r="N17" t="n">
+        <v>80</v>
+      </c>
+      <c r="O17" t="n">
+        <v>138</v>
+      </c>
+      <c r="P17" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Cooling|Twin</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>112.47</v>
+      </c>
+      <c r="D18" t="n">
+        <v>30</v>
+      </c>
+      <c r="E18" t="n">
+        <v>14</v>
+      </c>
+      <c r="F18" t="n">
+        <v>47</v>
+      </c>
+      <c r="G18" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I18" t="n">
+        <v>48</v>
+      </c>
+      <c r="J18" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="M18" t="n">
+        <v>94</v>
+      </c>
+      <c r="N18" t="n">
+        <v>70</v>
+      </c>
+      <c r="O18" t="n">
+        <v>51</v>
+      </c>
+      <c r="P18" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Cooling|California King</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>34.51</v>
+      </c>
+      <c r="D19" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" t="n">
+        <v>93</v>
+      </c>
+      <c r="G19" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="L19" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="M19" t="n">
+        <v>53</v>
+      </c>
+      <c r="N19" t="n">
+        <v>46</v>
+      </c>
+      <c r="O19" t="n">
+        <v>40</v>
+      </c>
+      <c r="P19" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Organic &amp; Natural</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bamboo</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>12098.02</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3843</v>
+      </c>
+      <c r="E21" t="n">
+        <v>565</v>
+      </c>
+      <c r="F21" t="n">
+        <v>40</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="I21" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="J21" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="M21" t="n">
+        <v>21</v>
+      </c>
+      <c r="N21" t="n">
+        <v>25</v>
+      </c>
+      <c r="O21" t="n">
+        <v>30</v>
+      </c>
+      <c r="P21" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bamboo|King</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1749.089999999999</v>
+      </c>
+      <c r="D22" t="n">
+        <v>427</v>
+      </c>
+      <c r="E22" t="n">
+        <v>185</v>
+      </c>
+      <c r="F22" t="n">
+        <v>45</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="J22" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="L22" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="M22" t="n">
+        <v>20</v>
+      </c>
+      <c r="N22" t="n">
+        <v>21</v>
+      </c>
+      <c r="O22" t="n">
+        <v>29</v>
+      </c>
+      <c r="P22" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>BOTH — short of traffic and under target</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Bamboo|Queen</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1320.28</v>
+      </c>
+      <c r="D23" t="n">
+        <v>470</v>
+      </c>
+      <c r="E23" t="n">
+        <v>123</v>
+      </c>
+      <c r="F23" t="n">
+        <v>28</v>
+      </c>
+      <c r="G23" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="I23" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="J23" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M23" t="n">
+        <v>18</v>
+      </c>
+      <c r="N23" t="n">
+        <v>29</v>
+      </c>
+      <c r="O23" t="n">
+        <v>35</v>
+      </c>
+      <c r="P23" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>BOTH — short of traffic and under target</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Cooling</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>930.33</v>
+      </c>
+      <c r="D24" t="n">
+        <v>337</v>
+      </c>
+      <c r="E24" t="n">
+        <v>16</v>
+      </c>
+      <c r="F24" t="n">
+        <v>49</v>
+      </c>
+      <c r="G24" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="L24" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="M24" t="n">
+        <v>52</v>
+      </c>
+      <c r="N24" t="n">
+        <v>52</v>
+      </c>
+      <c r="O24" t="n">
+        <v>55</v>
+      </c>
+      <c r="P24" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>BOTH — short of traffic and under target</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Bamboo|Full</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>615.8000000000002</v>
+      </c>
+      <c r="D25" t="n">
+        <v>147</v>
+      </c>
+      <c r="E25" t="n">
+        <v>91</v>
+      </c>
+      <c r="F25" t="n">
+        <v>64</v>
+      </c>
+      <c r="G25" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="J25" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="L25" t="n">
+        <v>5</v>
+      </c>
+      <c r="M25" t="n">
+        <v>27</v>
+      </c>
+      <c r="N25" t="n">
+        <v>17</v>
+      </c>
+      <c r="O25" t="n">
+        <v>20</v>
+      </c>
+      <c r="P25" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>BOTH — short of traffic and under target</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Size: Queen</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>575.89</v>
+      </c>
+      <c r="D26" t="n">
+        <v>313</v>
+      </c>
+      <c r="E26" t="n">
+        <v>243</v>
+      </c>
+      <c r="F26" t="n">
+        <v>30</v>
+      </c>
+      <c r="G26" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="I26" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="J26" t="n">
+        <v>17.52</v>
+      </c>
+      <c r="L26" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>PERFORMANCE GAP — shown, but CVR under target</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Size: King</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>488.5000000000001</v>
+      </c>
+      <c r="D27" t="n">
+        <v>238</v>
+      </c>
+      <c r="E27" t="n">
+        <v>310</v>
+      </c>
+      <c r="F27" t="n">
+        <v>43</v>
+      </c>
+      <c r="G27" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="I27" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="J27" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="L27" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>PERFORMANCE GAP — shown, but CVR under target</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Size: Full</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>277.87</v>
+      </c>
+      <c r="D28" t="n">
+        <v>136</v>
+      </c>
+      <c r="E28" t="n">
+        <v>163</v>
+      </c>
+      <c r="F28" t="n">
+        <v>51</v>
+      </c>
+      <c r="G28" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I28" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="J28" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="L28" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>PERFORMANCE GAP — shown, but CVR under target</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Bamboo|Cooling</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>246.98</v>
+      </c>
+      <c r="D29" t="n">
+        <v>87</v>
+      </c>
+      <c r="E29" t="n">
+        <v>14</v>
+      </c>
+      <c r="F29" t="n">
+        <v>18</v>
+      </c>
+      <c r="G29" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J29" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L29" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="M29" t="n">
+        <v>26</v>
+      </c>
+      <c r="N29" t="n">
+        <v>33</v>
+      </c>
+      <c r="O29" t="n">
+        <v>34</v>
+      </c>
+      <c r="P29" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Bamboo|Twin</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>215.66</v>
+      </c>
+      <c r="D30" t="n">
+        <v>72</v>
+      </c>
+      <c r="E30" t="n">
+        <v>20</v>
+      </c>
+      <c r="F30" t="n">
+        <v>29</v>
+      </c>
+      <c r="G30" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="L30" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="M30" t="n">
+        <v>7</v>
+      </c>
+      <c r="N30" t="n">
+        <v>15</v>
+      </c>
+      <c r="O30" t="n">
+        <v>20</v>
+      </c>
+      <c r="P30" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>PERFORMANCE GAP — shown, but CVR under target</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Cooling|Queen</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>156.76</v>
+      </c>
+      <c r="D31" t="n">
+        <v>46</v>
+      </c>
+      <c r="E31" t="n">
+        <v>16</v>
+      </c>
+      <c r="F31" t="n">
+        <v>48</v>
+      </c>
+      <c r="G31" t="n">
+        <v>16.59</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="L31" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="M31" t="n">
+        <v>38</v>
+      </c>
+      <c r="N31" t="n">
+        <v>67</v>
+      </c>
+      <c r="O31" t="n">
+        <v>81</v>
+      </c>
+      <c r="P31" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Cooling|King</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>152.01</v>
+      </c>
+      <c r="D32" t="n">
+        <v>47</v>
+      </c>
+      <c r="E32" t="n">
+        <v>12</v>
+      </c>
+      <c r="F32" t="n">
+        <v>40</v>
+      </c>
+      <c r="G32" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="J32" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="L32" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="M32" t="n">
+        <v>48</v>
+      </c>
+      <c r="N32" t="n">
+        <v>59</v>
+      </c>
+      <c r="O32" t="n">
+        <v>43</v>
+      </c>
+      <c r="P32" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Bamboo|California King</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>107.54</v>
+      </c>
+      <c r="D33" t="n">
+        <v>39</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="L33" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="M33" t="n">
+        <v>26</v>
+      </c>
+      <c r="N33" t="n">
+        <v>16</v>
+      </c>
+      <c r="O33" t="n">
+        <v>34</v>
+      </c>
+      <c r="P33" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Cooling|Full</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>86.13000000000001</v>
+      </c>
+      <c r="D34" t="n">
+        <v>22</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16</v>
+      </c>
+      <c r="F34" t="n">
+        <v>73</v>
+      </c>
+      <c r="G34" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="L34" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="N34" t="n">
+        <v>56</v>
+      </c>
+      <c r="O34" t="n">
+        <v>87</v>
+      </c>
+      <c r="P34" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>BOTH — short of traffic and under target</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Size: California King</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>65.81000000000002</v>
+      </c>
+      <c r="D35" t="n">
+        <v>30</v>
+      </c>
+      <c r="E35" t="n">
+        <v>12</v>
+      </c>
+      <c r="F35" t="n">
+        <v>17</v>
+      </c>
+      <c r="G35" t="n">
+        <v>21.69</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I35" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="J35" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="L35" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Size: Twin</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>41.60999999999999</v>
+      </c>
+      <c r="D36" t="n">
+        <v>19</v>
+      </c>
+      <c r="E36" t="n">
+        <v>37</v>
+      </c>
+      <c r="F36" t="n">
+        <v>33</v>
+      </c>
+      <c r="G36" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="J36" t="n">
+        <v>21.03</v>
+      </c>
+      <c r="L36" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>PERFORMANCE GAP — shown, but CVR under target</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Cooling|Twin</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>41.51</v>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="n">
+        <v>6</v>
+      </c>
+      <c r="F37" t="n">
+        <v>60</v>
+      </c>
+      <c r="G37" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="L37" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="M37" t="n">
+        <v>29</v>
+      </c>
+      <c r="N37" t="n">
+        <v>24</v>
+      </c>
+      <c r="O37" t="n">
+        <v>40</v>
+      </c>
+      <c r="P37" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Cooling|California King</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="D38" t="n">
+        <v>4</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" t="n">
+        <v>38</v>
+      </c>
+      <c r="G38" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="L38" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M38" t="n">
+        <v>37</v>
+      </c>
+      <c r="N38" t="n">
+        <v>28</v>
+      </c>
+      <c r="O38" t="n">
+        <v>31</v>
+      </c>
+      <c r="P38" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>NOT PRESENT at top of search</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/DBS4_Corrections_by_Situation_20260921-dbcd48b8.xlsx
+++ b/docs/DBS4_Corrections_by_Situation_20260921-dbcd48b8.xlsx
@@ -10,8 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ranking campaigns" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Other campaign types" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B4 keyword diagnosis" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B6 keyword diagnosis" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Syntax groups" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Syntax groups" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ranking campaigns'!$A$1:$Q$214</definedName>
@@ -18754,2526 +18753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="21" max="21"/>
-    <col width="80" customWidth="1" min="22" max="22"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Keyword</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Syntax</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Plan clicks/wk</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Weekly SV</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Clicks 30d</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>TOS clicks 30d</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>TOS clicks/day pre-deal</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>TOS clicks/day deal</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>TOS share</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>TOS CTR</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>CTR bar</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>TOS CVR</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>CVR bar</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>TOS impr. share</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Eff. TOS bid</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Organic</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Sponsored</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Rank 24 Jun</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Rank 14 Sep</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Rank 22 Sep</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Verdict</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Recommendation</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>bamboo sheets</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Bamboo</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>47605</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1036</v>
-      </c>
-      <c r="F2" t="n">
-        <v>382</v>
-      </c>
-      <c r="G2" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="H2" t="n">
-        <v>6</v>
-      </c>
-      <c r="I2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="L2" t="n">
-        <v>18.84</v>
-      </c>
-      <c r="M2" t="n">
-        <v>8.31</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="O2" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="P2" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>19</v>
-      </c>
-      <c r="R2" t="n">
-        <v>23</v>
-      </c>
-      <c r="S2" t="n">
-        <v>25</v>
-      </c>
-      <c r="T2" t="n">
-        <v>35</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>viscose bamboo sheets</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Bamboo</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>642</v>
-      </c>
-      <c r="E3" t="n">
-        <v>169</v>
-      </c>
-      <c r="F3" t="n">
-        <v>57</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>34</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="L3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="M3" t="n">
-        <v>8.31</v>
-      </c>
-      <c r="N3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O3" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="P3" t="n">
-        <v>12</v>
-      </c>
-      <c r="R3" t="n">
-        <v>16</v>
-      </c>
-      <c r="S3" t="n">
-        <v>13</v>
-      </c>
-      <c r="T3" t="n">
-        <v>13</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>king size bamboo sheets set</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bamboo|King</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>1367</v>
-      </c>
-      <c r="E4" t="n">
-        <v>128</v>
-      </c>
-      <c r="F4" t="n">
-        <v>47</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>37</v>
-      </c>
-      <c r="J4" t="n">
-        <v>7.19</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="L4" t="n">
-        <v>18.66</v>
-      </c>
-      <c r="M4" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="N4" t="n">
-        <v>7.13</v>
-      </c>
-      <c r="O4" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="P4" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R4" t="n">
-        <v>9</v>
-      </c>
-      <c r="S4" t="n">
-        <v>29</v>
-      </c>
-      <c r="T4" t="n">
-        <v>36</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>bamboo sheets queen size</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Bamboo|Queen</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>10342</v>
-      </c>
-      <c r="E5" t="n">
-        <v>166</v>
-      </c>
-      <c r="F5" t="n">
-        <v>38</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>23</v>
-      </c>
-      <c r="J5" t="n">
-        <v>5.92</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="L5" t="n">
-        <v>32.84</v>
-      </c>
-      <c r="M5" t="n">
-        <v>13.32</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="O5" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="P5" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4</v>
-      </c>
-      <c r="R5" t="n">
-        <v>28</v>
-      </c>
-      <c r="S5" t="n">
-        <v>32</v>
-      </c>
-      <c r="T5" t="n">
-        <v>32</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>bamboo bed sheets</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Bamboo</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>1564</v>
-      </c>
-      <c r="E6" t="n">
-        <v>44</v>
-      </c>
-      <c r="F6" t="n">
-        <v>35</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I6" t="n">
-        <v>78</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="L6" t="n">
-        <v>16.88</v>
-      </c>
-      <c r="M6" t="n">
-        <v>8.31</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="O6" t="n">
-        <v>6.58</v>
-      </c>
-      <c r="P6" t="n">
-        <v>40</v>
-      </c>
-      <c r="R6" t="n">
-        <v>31</v>
-      </c>
-      <c r="S6" t="n">
-        <v>31</v>
-      </c>
-      <c r="T6" t="n">
-        <v>27</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>bamboo sheets with corner straps</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Bamboo</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>115</v>
-      </c>
-      <c r="E7" t="n">
-        <v>75</v>
-      </c>
-      <c r="F7" t="n">
-        <v>29</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I7" t="n">
-        <v>39</v>
-      </c>
-      <c r="J7" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="L7" t="n">
-        <v>21.67</v>
-      </c>
-      <c r="M7" t="n">
-        <v>8.31</v>
-      </c>
-      <c r="N7" t="n">
-        <v>14.21</v>
-      </c>
-      <c r="O7" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="P7" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>23</v>
-      </c>
-      <c r="S7" t="n">
-        <v>13</v>
-      </c>
-      <c r="T7" t="n">
-        <v>14</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>ON TRACK</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Meets the CTR/CVR bars and wins TOS: scale while rank moves; if rank stalls, the gap is volume vs rivals — raise by the rank-gap step.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>queen sheet set bamboo</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Bamboo|Queen</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>366</v>
-      </c>
-      <c r="E8" t="n">
-        <v>97</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="M8" t="n">
-        <v>13.32</v>
-      </c>
-      <c r="P8" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>18</v>
-      </c>
-      <c r="S8" t="n">
-        <v>35</v>
-      </c>
-      <c r="T8" t="n">
-        <v>44</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>NOT PRESENT at top of search</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>bamboo king sheets</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Bamboo|King</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>1148</v>
-      </c>
-      <c r="E9" t="n">
-        <v>33</v>
-      </c>
-      <c r="F9" t="n">
-        <v>30</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>90</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="M9" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="N9" t="n">
-        <v>6.66</v>
-      </c>
-      <c r="O9" t="n">
-        <v>7.07</v>
-      </c>
-      <c r="P9" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>17</v>
-      </c>
-      <c r="R9" t="n">
-        <v>16</v>
-      </c>
-      <c r="S9" t="n">
-        <v>15</v>
-      </c>
-      <c r="T9" t="n">
-        <v>18</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>bamboo sheets full</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Bamboo|Full</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>1588</v>
-      </c>
-      <c r="E10" t="n">
-        <v>51</v>
-      </c>
-      <c r="F10" t="n">
-        <v>35</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="I10" t="n">
-        <v>69</v>
-      </c>
-      <c r="J10" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="M10" t="n">
-        <v>12.18</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="O10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="P10" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>7</v>
-      </c>
-      <c r="R10" t="n">
-        <v>58</v>
-      </c>
-      <c r="S10" t="n">
-        <v>13</v>
-      </c>
-      <c r="T10" t="n">
-        <v>11</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>king bamboo sheets</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Bamboo|King</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>1355</v>
-      </c>
-      <c r="E11" t="n">
-        <v>59</v>
-      </c>
-      <c r="F11" t="n">
-        <v>12</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>21</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="M11" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="P11" t="n">
-        <v>32</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>9</v>
-      </c>
-      <c r="R11" t="n">
-        <v>23</v>
-      </c>
-      <c r="S11" t="n">
-        <v>31</v>
-      </c>
-      <c r="T11" t="n">
-        <v>40</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>BOTH — short of traffic and under target</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Fix the offer first, then buy traffic: a small TOS probe (+10%) only while the CTR/CVR fix is made.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>bamboo sheets king size</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Bamboo|King</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>6945</v>
-      </c>
-      <c r="E12" t="n">
-        <v>54</v>
-      </c>
-      <c r="F12" t="n">
-        <v>17</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I12" t="n">
-        <v>32</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="M12" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="O12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P12" t="n">
-        <v>37</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>19</v>
-      </c>
-      <c r="R12" t="n">
-        <v>15</v>
-      </c>
-      <c r="S12" t="n">
-        <v>36</v>
-      </c>
-      <c r="T12" t="n">
-        <v>38</v>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>red bamboo sheets</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>53</v>
-      </c>
-      <c r="F13" t="n">
-        <v>25</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I13" t="n">
-        <v>45</v>
-      </c>
-      <c r="J13" t="n">
-        <v>8.960000000000001</v>
-      </c>
-      <c r="L13" t="n">
-        <v>16.57</v>
-      </c>
-      <c r="N13" t="n">
-        <v>26.58</v>
-      </c>
-      <c r="O13" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>black bamboo sheets</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Bamboo</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>463</v>
-      </c>
-      <c r="E14" t="n">
-        <v>30</v>
-      </c>
-      <c r="F14" t="n">
-        <v>19</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I14" t="n">
-        <v>62</v>
-      </c>
-      <c r="J14" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="M14" t="n">
-        <v>8.31</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O14" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="P14" t="n">
-        <v>13</v>
-      </c>
-      <c r="R14" t="n">
-        <v>18</v>
-      </c>
-      <c r="S14" t="n">
-        <v>21</v>
-      </c>
-      <c r="T14" t="n">
-        <v>17</v>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>bamboo cooling sheets</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Bamboo|Cooling</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>3233</v>
-      </c>
-      <c r="E15" t="n">
-        <v>44</v>
-      </c>
-      <c r="F15" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I15" t="n">
-        <v>7</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="L15" t="n">
-        <v>17.26</v>
-      </c>
-      <c r="M15" t="n">
-        <v>7.71</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="P15" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>17</v>
-      </c>
-      <c r="R15" t="n">
-        <v>30</v>
-      </c>
-      <c r="S15" t="n">
-        <v>35</v>
-      </c>
-      <c r="T15" t="n">
-        <v>27</v>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>NOT PRESENT at top of search</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>bamboo sheet set</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Bamboo</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>545</v>
-      </c>
-      <c r="E16" t="n">
-        <v>31</v>
-      </c>
-      <c r="F16" t="n">
-        <v>16</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>51</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="M16" t="n">
-        <v>8.31</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="O16" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="P16" t="n">
-        <v>58</v>
-      </c>
-      <c r="R16" t="n">
-        <v>22</v>
-      </c>
-      <c r="S16" t="n">
-        <v>48</v>
-      </c>
-      <c r="T16" t="n">
-        <v>38</v>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>burgundy sheets queen</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>352</v>
-      </c>
-      <c r="E17" t="n">
-        <v>27</v>
-      </c>
-      <c r="F17" t="n">
-        <v>9</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I17" t="n">
-        <v>33</v>
-      </c>
-      <c r="P17" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>5</v>
-      </c>
-      <c r="R17" t="n">
-        <v>47</v>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>NOT PRESENT at top of search</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>full bamboo sheets</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Bamboo|Full</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>200</v>
-      </c>
-      <c r="E18" t="n">
-        <v>22</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I18" t="n">
-        <v>45</v>
-      </c>
-      <c r="J18" t="n">
-        <v>8.039999999999999</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="M18" t="n">
-        <v>12.18</v>
-      </c>
-      <c r="N18" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="O18" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="P18" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>15</v>
-      </c>
-      <c r="S18" t="n">
-        <v>12</v>
-      </c>
-      <c r="T18" t="n">
-        <v>13</v>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>bamboo twin sheets</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Bamboo|Twin</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>417</v>
-      </c>
-      <c r="E19" t="n">
-        <v>20</v>
-      </c>
-      <c r="F19" t="n">
-        <v>7</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>35</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="M19" t="n">
-        <v>10.95</v>
-      </c>
-      <c r="P19" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>18</v>
-      </c>
-      <c r="R19" t="n">
-        <v>13</v>
-      </c>
-      <c r="S19" t="n">
-        <v>28</v>
-      </c>
-      <c r="T19" t="n">
-        <v>25</v>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>bamboo full size bed sheets</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Bamboo|Full</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>197</v>
-      </c>
-      <c r="E20" t="n">
-        <v>14</v>
-      </c>
-      <c r="F20" t="n">
-        <v>13</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I20" t="n">
-        <v>89</v>
-      </c>
-      <c r="J20" t="n">
-        <v>10.83</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="L20" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="M20" t="n">
-        <v>12.18</v>
-      </c>
-      <c r="P20" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>20</v>
-      </c>
-      <c r="R20" t="n">
-        <v>36</v>
-      </c>
-      <c r="S20" t="n">
-        <v>25</v>
-      </c>
-      <c r="T20" t="n">
-        <v>26</v>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>bamboo sheets queen</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Bamboo|Queen</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>858</v>
-      </c>
-      <c r="E21" t="n">
-        <v>37</v>
-      </c>
-      <c r="F21" t="n">
-        <v>7</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>20</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="M21" t="n">
-        <v>13.32</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="P21" t="n">
-        <v>63</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>8</v>
-      </c>
-      <c r="R21" t="n">
-        <v>18</v>
-      </c>
-      <c r="S21" t="n">
-        <v>39</v>
-      </c>
-      <c r="T21" t="n">
-        <v>55</v>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>NOT PRESENT at top of search</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>sheets queen size bed set</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>23315</v>
-      </c>
-      <c r="E22" t="n">
-        <v>41</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>3</v>
-      </c>
-      <c r="L22" t="n">
-        <v>18.52</v>
-      </c>
-      <c r="P22" t="n">
-        <v>71</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>17</v>
-      </c>
-      <c r="R22" t="n">
-        <v>48</v>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>NOT PRESENT at top of search</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>cooling bed sheets</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Cooling</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>5185</v>
-      </c>
-      <c r="E23" t="n">
-        <v>20</v>
-      </c>
-      <c r="F23" t="n">
-        <v>12</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I23" t="n">
-        <v>59</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="M23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="P23" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>22</v>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>NOT PRESENT at top of search</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>twin sheets bamboo</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Bamboo|Twin</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>203</v>
-      </c>
-      <c r="E24" t="n">
-        <v>21</v>
-      </c>
-      <c r="F24" t="n">
-        <v>8</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>38</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="M24" t="n">
-        <v>10.95</v>
-      </c>
-      <c r="P24" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>NOT PRESENT at top of search</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>bamboo sheets pink</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>29</v>
-      </c>
-      <c r="F25" t="n">
-        <v>3</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>11</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>full size bamboo sheets</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Bamboo|Full</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>460</v>
-      </c>
-      <c r="E26" t="n">
-        <v>18</v>
-      </c>
-      <c r="F26" t="n">
-        <v>8</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>46</v>
-      </c>
-      <c r="J26" t="n">
-        <v>6.58</v>
-      </c>
-      <c r="K26" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="M26" t="n">
-        <v>12.18</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O26" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="P26" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>15</v>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>bamboo viscose sheets queen size</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Bamboo|Queen</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>124</v>
-      </c>
-      <c r="E27" t="n">
-        <v>15</v>
-      </c>
-      <c r="F27" t="n">
-        <v>9</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>59</v>
-      </c>
-      <c r="J27" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="M27" t="n">
-        <v>13.32</v>
-      </c>
-      <c r="P27" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>bamboo sheets twin</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Bamboo|Twin</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>714</v>
-      </c>
-      <c r="E28" t="n">
-        <v>26</v>
-      </c>
-      <c r="F28" t="n">
-        <v>2</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>9</v>
-      </c>
-      <c r="K28" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="M28" t="n">
-        <v>10.95</v>
-      </c>
-      <c r="P28" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>24</v>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>NOT PRESENT at top of search</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>100% bamboo sheets king size</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Bamboo|King</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>260</v>
-      </c>
-      <c r="E29" t="n">
-        <v>18</v>
-      </c>
-      <c r="F29" t="n">
-        <v>4</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I29" t="n">
-        <v>24</v>
-      </c>
-      <c r="J29" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="M29" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="P29" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>15</v>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>king bamboo sheets deep pocket</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Bamboo|King</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>355</v>
-      </c>
-      <c r="E30" t="n">
-        <v>13</v>
-      </c>
-      <c r="F30" t="n">
-        <v>6</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>43</v>
-      </c>
-      <c r="J30" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="K30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="M30" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="P30" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>bamboo sheet sets</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Bamboo</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>121</v>
-      </c>
-      <c r="E31" t="n">
-        <v>10</v>
-      </c>
-      <c r="F31" t="n">
-        <v>6</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>56</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="M31" t="n">
-        <v>8.31</v>
-      </c>
-      <c r="N31" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="O31" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="P31" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>12</v>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>NOT PRESENT at top of search</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>queen bamboo sheet set</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Bamboo|Queen</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>1397</v>
-      </c>
-      <c r="E32" t="n">
-        <v>15</v>
-      </c>
-      <c r="F32" t="n">
-        <v>7</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I32" t="n">
-        <v>48</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="M32" t="n">
-        <v>13.32</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="O32" t="n">
-        <v>6.07</v>
-      </c>
-      <c r="P32" t="n">
-        <v>21</v>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>NOT PRESENT at top of search</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>queen size sheets bamboo</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Bamboo|Queen</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>107</v>
-      </c>
-      <c r="E33" t="n">
-        <v>7</v>
-      </c>
-      <c r="F33" t="n">
-        <v>7</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I33" t="n">
-        <v>100</v>
-      </c>
-      <c r="K33" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="M33" t="n">
-        <v>13.32</v>
-      </c>
-      <c r="P33" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>3</v>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>NOT PRESENT at top of search</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>king bed bamboo sheets</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Bamboo|King</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>319</v>
-      </c>
-      <c r="E34" t="n">
-        <v>11</v>
-      </c>
-      <c r="F34" t="n">
-        <v>5</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I34" t="n">
-        <v>49</v>
-      </c>
-      <c r="J34" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="M34" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="P34" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>27</v>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>cooling bed sheets king</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Cooling|King</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>492</v>
-      </c>
-      <c r="E35" t="n">
-        <v>8</v>
-      </c>
-      <c r="F35" t="n">
-        <v>7</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I35" t="n">
-        <v>90</v>
-      </c>
-      <c r="J35" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="K35" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="M35" t="n">
-        <v>10.53</v>
-      </c>
-      <c r="P35" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>11</v>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>bamboo sheets california king</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Bamboo|California King</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>420</v>
-      </c>
-      <c r="E36" t="n">
-        <v>17</v>
-      </c>
-      <c r="F36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>5</v>
-      </c>
-      <c r="K36" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="M36" t="n">
-        <v>8.85</v>
-      </c>
-      <c r="N36" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="O36" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="P36" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>6</v>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>NOT PRESENT at top of search</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>queen sheets set bamboo</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>18</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>2</v>
-      </c>
-      <c r="N37" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="O37" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>NOT PRESENT at top of search</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>bamboo sheets king</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Bamboo|King</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>2680</v>
-      </c>
-      <c r="E38" t="n">
-        <v>11</v>
-      </c>
-      <c r="F38" t="n">
-        <v>8</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>74</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="M38" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="N38" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="O38" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="P38" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>19</v>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>NOT PRESENT at top of search</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>bamboo king size sheets</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Bamboo|King</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>132</v>
-      </c>
-      <c r="E39" t="n">
-        <v>8</v>
-      </c>
-      <c r="F39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I39" t="n">
-        <v>67</v>
-      </c>
-      <c r="K39" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="M39" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="P39" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>17</v>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>NOT PRESENT at top of search</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>extra deep 20-24 inch pocket king size bamboo sheets</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Bamboo|King</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>175</v>
-      </c>
-      <c r="E40" t="n">
-        <v>8</v>
-      </c>
-      <c r="F40" t="n">
-        <v>7</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I40" t="n">
-        <v>91</v>
-      </c>
-      <c r="K40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="P40" t="n">
-        <v>93</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2</v>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>NOT PRESENT at top of search</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Eligibility first: confirm the exact campaign is enabled and its TOS price clears the group market limit; then push +25% on TOS and read in 3 days.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>king sheets bamboo</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Bamboo|King</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>766</v>
-      </c>
-      <c r="E41" t="n">
-        <v>10</v>
-      </c>
-      <c r="F41" t="n">
-        <v>5</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I41" t="n">
-        <v>46</v>
-      </c>
-      <c r="J41" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="K41" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="M41" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="N41" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="O41" t="n">
-        <v>7.93</v>
-      </c>
-      <c r="P41" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>25</v>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Buy the traffic: it converts at top of search. Raise the TOS modifier by the rank-gap step, lift budget if it caps, and hold base so PDP does not grow.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q38"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -22356,969 +19836,6 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Bamboo</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>12098.02</v>
-      </c>
-      <c r="D21" t="n">
-        <v>3843</v>
-      </c>
-      <c r="E21" t="n">
-        <v>565</v>
-      </c>
-      <c r="F21" t="n">
-        <v>40</v>
-      </c>
-      <c r="G21" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="I21" t="n">
-        <v>17.57</v>
-      </c>
-      <c r="J21" t="n">
-        <v>8.31</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L21" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="M21" t="n">
-        <v>21</v>
-      </c>
-      <c r="N21" t="n">
-        <v>25</v>
-      </c>
-      <c r="O21" t="n">
-        <v>30</v>
-      </c>
-      <c r="P21" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Bamboo|King</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1749.089999999999</v>
-      </c>
-      <c r="D22" t="n">
-        <v>427</v>
-      </c>
-      <c r="E22" t="n">
-        <v>185</v>
-      </c>
-      <c r="F22" t="n">
-        <v>45</v>
-      </c>
-      <c r="G22" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="I22" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="J22" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="K22" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="L22" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="M22" t="n">
-        <v>20</v>
-      </c>
-      <c r="N22" t="n">
-        <v>21</v>
-      </c>
-      <c r="O22" t="n">
-        <v>29</v>
-      </c>
-      <c r="P22" t="n">
-        <v>35</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>BOTH — short of traffic and under target</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Bamboo|Queen</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1320.28</v>
-      </c>
-      <c r="D23" t="n">
-        <v>470</v>
-      </c>
-      <c r="E23" t="n">
-        <v>123</v>
-      </c>
-      <c r="F23" t="n">
-        <v>28</v>
-      </c>
-      <c r="G23" t="n">
-        <v>7.78</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="I23" t="n">
-        <v>10.24</v>
-      </c>
-      <c r="J23" t="n">
-        <v>13.32</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="L23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="M23" t="n">
-        <v>18</v>
-      </c>
-      <c r="N23" t="n">
-        <v>29</v>
-      </c>
-      <c r="O23" t="n">
-        <v>35</v>
-      </c>
-      <c r="P23" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>BOTH — short of traffic and under target</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Cooling</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>930.33</v>
-      </c>
-      <c r="D24" t="n">
-        <v>337</v>
-      </c>
-      <c r="E24" t="n">
-        <v>16</v>
-      </c>
-      <c r="F24" t="n">
-        <v>49</v>
-      </c>
-      <c r="G24" t="n">
-        <v>11.01</v>
-      </c>
-      <c r="H24" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L24" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="M24" t="n">
-        <v>52</v>
-      </c>
-      <c r="N24" t="n">
-        <v>52</v>
-      </c>
-      <c r="O24" t="n">
-        <v>55</v>
-      </c>
-      <c r="P24" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>BOTH — short of traffic and under target</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Bamboo|Full</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>615.8000000000002</v>
-      </c>
-      <c r="D25" t="n">
-        <v>147</v>
-      </c>
-      <c r="E25" t="n">
-        <v>91</v>
-      </c>
-      <c r="F25" t="n">
-        <v>64</v>
-      </c>
-      <c r="G25" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="H25" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="I25" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="J25" t="n">
-        <v>12.18</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="L25" t="n">
-        <v>5</v>
-      </c>
-      <c r="M25" t="n">
-        <v>27</v>
-      </c>
-      <c r="N25" t="n">
-        <v>17</v>
-      </c>
-      <c r="O25" t="n">
-        <v>20</v>
-      </c>
-      <c r="P25" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>BOTH — short of traffic and under target</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Size: Queen</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>575.89</v>
-      </c>
-      <c r="D26" t="n">
-        <v>313</v>
-      </c>
-      <c r="E26" t="n">
-        <v>243</v>
-      </c>
-      <c r="F26" t="n">
-        <v>30</v>
-      </c>
-      <c r="G26" t="n">
-        <v>7.38</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="I26" t="n">
-        <v>11.18</v>
-      </c>
-      <c r="J26" t="n">
-        <v>17.52</v>
-      </c>
-      <c r="L26" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>PERFORMANCE GAP — shown, but CVR under target</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Size: King</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>488.5000000000001</v>
-      </c>
-      <c r="D27" t="n">
-        <v>238</v>
-      </c>
-      <c r="E27" t="n">
-        <v>310</v>
-      </c>
-      <c r="F27" t="n">
-        <v>43</v>
-      </c>
-      <c r="G27" t="n">
-        <v>8.24</v>
-      </c>
-      <c r="H27" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="I27" t="n">
-        <v>10.53</v>
-      </c>
-      <c r="J27" t="n">
-        <v>13.23</v>
-      </c>
-      <c r="L27" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>PERFORMANCE GAP — shown, but CVR under target</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Size: Full</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>277.87</v>
-      </c>
-      <c r="D28" t="n">
-        <v>136</v>
-      </c>
-      <c r="E28" t="n">
-        <v>163</v>
-      </c>
-      <c r="F28" t="n">
-        <v>51</v>
-      </c>
-      <c r="G28" t="n">
-        <v>10.29</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="I28" t="n">
-        <v>6.68</v>
-      </c>
-      <c r="J28" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="L28" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>PERFORMANCE GAP — shown, but CVR under target</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Bamboo|Cooling</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>246.98</v>
-      </c>
-      <c r="D29" t="n">
-        <v>87</v>
-      </c>
-      <c r="E29" t="n">
-        <v>14</v>
-      </c>
-      <c r="F29" t="n">
-        <v>18</v>
-      </c>
-      <c r="G29" t="n">
-        <v>14.83</v>
-      </c>
-      <c r="H29" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="I29" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="J29" t="n">
-        <v>7.71</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L29" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="M29" t="n">
-        <v>26</v>
-      </c>
-      <c r="N29" t="n">
-        <v>33</v>
-      </c>
-      <c r="O29" t="n">
-        <v>34</v>
-      </c>
-      <c r="P29" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>NOT PRESENT at top of search</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Bamboo|Twin</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>215.66</v>
-      </c>
-      <c r="D30" t="n">
-        <v>72</v>
-      </c>
-      <c r="E30" t="n">
-        <v>20</v>
-      </c>
-      <c r="F30" t="n">
-        <v>29</v>
-      </c>
-      <c r="G30" t="n">
-        <v>6.73</v>
-      </c>
-      <c r="H30" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>10.95</v>
-      </c>
-      <c r="L30" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="M30" t="n">
-        <v>7</v>
-      </c>
-      <c r="N30" t="n">
-        <v>15</v>
-      </c>
-      <c r="O30" t="n">
-        <v>20</v>
-      </c>
-      <c r="P30" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>PERFORMANCE GAP — shown, but CVR under target</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Cooling|Queen</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>156.76</v>
-      </c>
-      <c r="D31" t="n">
-        <v>46</v>
-      </c>
-      <c r="E31" t="n">
-        <v>16</v>
-      </c>
-      <c r="F31" t="n">
-        <v>48</v>
-      </c>
-      <c r="G31" t="n">
-        <v>16.59</v>
-      </c>
-      <c r="H31" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="L31" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="M31" t="n">
-        <v>38</v>
-      </c>
-      <c r="N31" t="n">
-        <v>67</v>
-      </c>
-      <c r="O31" t="n">
-        <v>81</v>
-      </c>
-      <c r="P31" t="n">
-        <v>75</v>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>NOT PRESENT at top of search</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Cooling|King</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>152.01</v>
-      </c>
-      <c r="D32" t="n">
-        <v>47</v>
-      </c>
-      <c r="E32" t="n">
-        <v>12</v>
-      </c>
-      <c r="F32" t="n">
-        <v>40</v>
-      </c>
-      <c r="G32" t="n">
-        <v>7.51</v>
-      </c>
-      <c r="H32" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="J32" t="n">
-        <v>10.53</v>
-      </c>
-      <c r="L32" t="n">
-        <v>5.54</v>
-      </c>
-      <c r="M32" t="n">
-        <v>48</v>
-      </c>
-      <c r="N32" t="n">
-        <v>59</v>
-      </c>
-      <c r="O32" t="n">
-        <v>43</v>
-      </c>
-      <c r="P32" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>TRAFFIC GAP — converts when shown, not shown/clicked enough</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Bamboo|California King</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>107.54</v>
-      </c>
-      <c r="D33" t="n">
-        <v>39</v>
-      </c>
-      <c r="E33" t="n">
-        <v>2</v>
-      </c>
-      <c r="F33" t="n">
-        <v>5</v>
-      </c>
-      <c r="G33" t="n">
-        <v>6.66</v>
-      </c>
-      <c r="H33" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>8.85</v>
-      </c>
-      <c r="K33" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="L33" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="M33" t="n">
-        <v>26</v>
-      </c>
-      <c r="N33" t="n">
-        <v>16</v>
-      </c>
-      <c r="O33" t="n">
-        <v>34</v>
-      </c>
-      <c r="P33" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>NOT PRESENT at top of search</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Cooling|Full</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>86.13000000000001</v>
-      </c>
-      <c r="D34" t="n">
-        <v>22</v>
-      </c>
-      <c r="E34" t="n">
-        <v>16</v>
-      </c>
-      <c r="F34" t="n">
-        <v>73</v>
-      </c>
-      <c r="G34" t="n">
-        <v>10.27</v>
-      </c>
-      <c r="H34" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>12.42</v>
-      </c>
-      <c r="L34" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="N34" t="n">
-        <v>56</v>
-      </c>
-      <c r="O34" t="n">
-        <v>87</v>
-      </c>
-      <c r="P34" t="n">
-        <v>87</v>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>BOTH — short of traffic and under target</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Size: California King</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>65.81000000000002</v>
-      </c>
-      <c r="D35" t="n">
-        <v>30</v>
-      </c>
-      <c r="E35" t="n">
-        <v>12</v>
-      </c>
-      <c r="F35" t="n">
-        <v>17</v>
-      </c>
-      <c r="G35" t="n">
-        <v>21.69</v>
-      </c>
-      <c r="H35" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="I35" t="n">
-        <v>6.12</v>
-      </c>
-      <c r="J35" t="n">
-        <v>15.78</v>
-      </c>
-      <c r="L35" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>NOT PRESENT at top of search</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Size: Twin</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>41.60999999999999</v>
-      </c>
-      <c r="D36" t="n">
-        <v>19</v>
-      </c>
-      <c r="E36" t="n">
-        <v>37</v>
-      </c>
-      <c r="F36" t="n">
-        <v>33</v>
-      </c>
-      <c r="G36" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="H36" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="I36" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="J36" t="n">
-        <v>21.03</v>
-      </c>
-      <c r="L36" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>PERFORMANCE GAP — shown, but CVR under target</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Cooling|Twin</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>41.51</v>
-      </c>
-      <c r="D37" t="n">
-        <v>10</v>
-      </c>
-      <c r="E37" t="n">
-        <v>6</v>
-      </c>
-      <c r="F37" t="n">
-        <v>60</v>
-      </c>
-      <c r="G37" t="n">
-        <v>6.77</v>
-      </c>
-      <c r="H37" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>13.95</v>
-      </c>
-      <c r="L37" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="M37" t="n">
-        <v>29</v>
-      </c>
-      <c r="N37" t="n">
-        <v>24</v>
-      </c>
-      <c r="O37" t="n">
-        <v>40</v>
-      </c>
-      <c r="P37" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>NOT PRESENT at top of search</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Cooling|California King</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>11.88</v>
-      </c>
-      <c r="D38" t="n">
-        <v>4</v>
-      </c>
-      <c r="E38" t="n">
-        <v>2</v>
-      </c>
-      <c r="F38" t="n">
-        <v>38</v>
-      </c>
-      <c r="G38" t="n">
-        <v>7.88</v>
-      </c>
-      <c r="H38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="L38" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="M38" t="n">
-        <v>37</v>
-      </c>
-      <c r="N38" t="n">
-        <v>28</v>
-      </c>
-      <c r="O38" t="n">
-        <v>31</v>
-      </c>
-      <c r="P38" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>NOT PRESENT at top of search</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DBS4_Corrections_by_Situation_20260921-dbcd48b8.xlsx
+++ b/docs/DBS4_Corrections_by_Situation_20260921-dbcd48b8.xlsx
@@ -601,7 +601,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $5.97 → $7.46; base −25% for product pages at 56% (d14): base $2.53 → $1.90; modifier 293%; daily read to 09-28</t>
+          <t>Push TOS +20% (no click requirement on file → +20% (a stated departure: the logic document would hold at the ceiling)): $5.97 → $7.16; base −25% for product pages at 56% (d14): base $2.53 → $1.90; modifier 278%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -668,86 +668,83 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $2.66 → $3.32; base −25% for product pages at 96% (d14): base $1.43 → $1.07; modifier 210%; daily read to 09-28</t>
+          <t>Push TOS +10% (no click requirement on file → +20% (a stated departure: the logic document would hold at the ceiling); halved — impression share did not rise after the 15 Sep raise (4.1% → 3.7%)): $2.66 → $2.93; base −25% for product pages at 96% (d14): base $1.43 → $1.07; modifier 173%; daily read to 09-28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A · In focus — delivering, hold</t>
+          <t>A · In focus — keyword paused (duplicate)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>King Cooling Sheets-[Cooling|King]-(MSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Bamboo Sheets-[Bamboo]-(VHSV)-Exact-(Ranking)-DO-BAMBOO-KING-CREME</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>IN · Cooling|King</t>
+          <t>IN · Bamboo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MSV</t>
+          <t>VHSV</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5.18</v>
+        <v>6.32</v>
       </c>
       <c r="F4" t="n">
-        <v>252</v>
+        <v>145</v>
       </c>
       <c r="G4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.503</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>— → 33 → 12</t>
+          <t>29 → 33 → 10</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="O4" t="n">
-        <v>5.93</v>
+        <v>0</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>budget $13→$16.9</t>
+          <t>mod 39→47%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Delivering its clicks — hold; evaluate cost per click after the deal</t>
+          <t>Keyword paused; term runs in the flagship — leave paused</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A · In focus — keyword paused (duplicate)</t>
+          <t>A · In focus — push + investigate</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bamboo Sheets-[Bamboo]-(VHSV)-Exact-(Ranking)-DO-BAMBOO-KING-CREME</t>
+          <t>Bamboo Bed Sheets-[Bamboo]-(MSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -757,23 +754,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VHSV</t>
+          <t>MSV</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>6.32</v>
       </c>
       <c r="F5" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="n">
-        <v>0.503</v>
-      </c>
       <c r="I5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -783,23 +777,26 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>45 → 24 → 10</t>
+          <t>27 → 42 → 7</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
+      <c r="O5" t="n">
+        <v>3.41</v>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>mod 39→47%</t>
+          <t>holds</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Keyword paused; term runs in the flagship — leave paused</t>
+          <t>Push TOS +30% (0% of required top-of-search clicks delivered → +30%): $3.41 → $4.43; modifier 235%; investigate the rank loss the same day; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -811,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bamboo Bed Sheets-[Bamboo]-(MSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Bamboo Sheets Queen-[Bamboo|Queen]-(MSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IN · Bamboo</t>
+          <t>IN · Bamboo|Queen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -825,36 +822,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6.32</v>
+        <v>6.39</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1356</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>101</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.96</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>30 → 42 → 7</t>
+          <t>54 → 71 → 6</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="O6" t="n">
-        <v>3.41</v>
+        <v>3.75</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 42 vs target 7: more than 2× the target → +30%): $3.41 → $4.43; modifier 235%; investigate the rank loss the same day; daily read to 09-28</t>
+          <t>Push TOS +15% (0% of required top-of-search clicks delivered → +30%; halved — impression share did not rise after the 15 Sep raise (0.0% → 0.0%)): $3.75 → $4.31; base −25% for product pages at 96% (d14): base $2.26 → $1.69; modifier 155%; investigate the rank loss the same day; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -875,62 +875,62 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bamboo Sheets Queen-[Bamboo|Queen]-(MSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
+          <t>King Size Bamboo Sheet Sets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>IN · Bamboo|Queen</t>
+          <t>IN · Bamboo|King</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6.39</v>
+        <v>6.47</v>
       </c>
       <c r="F7" t="n">
-        <v>1356</v>
+        <v>405</v>
       </c>
       <c r="G7" t="n">
-        <v>101</v>
+        <v>30</v>
       </c>
       <c r="H7" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="K7" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>48 → 62 → 6</t>
+          <t>26 → 42 → 9</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="N7" t="n">
-        <v>0.15</v>
+        <v>1.01</v>
       </c>
       <c r="O7" t="n">
-        <v>3.75</v>
+        <v>9.33</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>holds</t>
+          <t>mod 502→568%; base ↓10%; TOS $9.33→$9.35</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 62 vs target 6: more than 2× the target → +30%): $3.75 → $4.88; base −25% for product pages at 96% (d14): base $2.26 → $1.69; modifier 188%; investigate the rank loss the same day; daily read to 09-28</t>
+          <t>Push TOS +0% (114% of required top-of-search clicks delivered — at requirement, no step; evaluate cost per click after the deal): $9.33 → $9.33; modifier 502%; budget $32.00 → $41.60; investigate the rank loss the same day; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -942,62 +942,62 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>King Size Bamboo Sheet Sets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Queen Bamboo Bed Sheet Sets-[Bamboo|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IN · Bamboo|King</t>
+          <t>IN · Bamboo|Queen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6.47</v>
+        <v>6.39</v>
       </c>
       <c r="F8" t="n">
-        <v>405</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>3.8</v>
+        <v>0.1</v>
       </c>
       <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>46 → 60 → 8</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
         <v>10</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>22 → 40 → 9</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>32</v>
-      </c>
       <c r="N8" t="n">
-        <v>1.01</v>
+        <v>0.09</v>
       </c>
       <c r="O8" t="n">
-        <v>9.33</v>
+        <v>6.29</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>mod 502→568%; base ↓10%; TOS $9.33→$9.35</t>
+          <t>mod 231→236%; TOS $6.29→$6.38</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 40 vs target 9: more than 2× the target → +30%): $9.33 → $12.13; modifier 683%; budget $32.00 → $41.60; investigate the rank loss the same day; daily read to 09-28</t>
+          <t>Push TOS +30% (12% of required top-of-search clicks delivered → +30%): $6.29 → $8.18; modifier 330%; investigate the rank loss the same day; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Queen Bamboo Bed Sheet Sets-[Bamboo|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
+          <t>Queen Bamboo Sheet Set-(MSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-TAUPE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1019,52 +1019,52 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>MSV</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>6.39</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>162</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.796</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>46 → 60 → 8</t>
+          <t>24 → 35 → 7</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>10</v>
+        <v>12.86</v>
       </c>
       <c r="N9" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>6.29</v>
+        <v>3.8</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>mod 231→236%; TOS $6.29→$6.38</t>
+          <t>mod 166→230%; TOS $3.80→$4.72</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 60 vs target 8: more than 2× the target → +30%): $6.29 → $8.18; modifier 330%; investigate the rank loss the same day; daily read to 09-28</t>
+          <t>Push TOS +15% (0% of required top-of-search clicks delivered → +30%; halved — impression share did not rise after the 15 Sep raise (0.1% → 0.0%)): $3.80 → $4.37; modifier 206%; investigate the rank loss the same day; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $4.69 → $5.87; modifier 209%; daily read to 09-28</t>
+          <t>Push TOS +30% (0% of required top-of-search clicks delivered → +30%): $4.69 → $6.10; modifier 221%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $9.10 → $11.38; modifier 355%; budget $5.00 → $6.50; re-point the ad to the serving child; daily read to 09-28</t>
+          <t>Push TOS +20% (no click requirement on file → +20% (a stated departure: the logic document would hold at the ceiling)): $9.10 → $10.92; modifier 337%; budget $5.00 → $6.50; re-point the ad to the serving child; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 24 vs target 1: more than 2× the target → +30%): $3.20 → $4.15; modifier 206%; daily read to 09-28</t>
+          <t>Push TOS +30% (3% of required top-of-search clicks delivered → +30%): $3.20 → $4.15; modifier 206%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 29 vs target 9: more than 2× the target → +30%): $4.79 → $6.23; modifier 297%; daily read to 09-28</t>
+          <t>Push TOS +30% (15% of required top-of-search clicks delivered → +30%): $4.79 → $6.23; modifier 297%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $2.67 → $3.33; modifier 94%; daily read to 09-28</t>
+          <t>Push TOS +10% (no click requirement on file → +20% (a stated departure: the logic document would hold at the ceiling); halved — impression share did not rise after the 15 Sep raise (0.0% → 0.0%)): $2.67 → $2.93; modifier 71%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 41 vs target 8: more than 2× the target → +30%): $5.10 → $6.63; modifier 322%; daily read to 09-28</t>
+          <t>Push TOS +30% (22% of required top-of-search clicks delivered → +30%): $5.10 → $6.63; modifier 322%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 40 vs target 1: more than 2× the target → +30%): $5.10 → $6.63; modifier 322%; daily read to 09-28</t>
+          <t>Push TOS +30% (2% of required top-of-search clicks delivered → +30%): $5.10 → $6.63; modifier 322%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 36 vs target 1: more than 2× the target → +30%): $6.84 → $8.89; modifier 220%; daily read to 09-28</t>
+          <t>Push TOS +30% (7% of required top-of-search clicks delivered → +30%): $6.84 → $8.89; modifier 220%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $6.41 → $8.01; modifier 410%; daily read to 09-28</t>
+          <t>Push TOS +30% (0% of required top-of-search clicks delivered → +30%): $6.41 → $8.33; modifier 430%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $4.73 → $5.91; modifier 308%; daily read to 09-28</t>
+          <t>Push TOS +20% (no click requirement on file → +20% (a stated departure: the logic document would hold at the ceiling)): $4.73 → $5.67; modifier 291%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Push TOS +10% (rank 12 vs target 8: within 5 positions → +10%): $8.27 → $9.10; modifier 364%; budget $11.01 → $14.31; daily read to 09-28</t>
+          <t>Push TOS +0% (126% of required top-of-search clicks delivered — at requirement, no step; evaluate cost per click after the deal): $8.27 → $8.27; modifier 322%; budget $11.01 → $14.31; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 40 vs target 6: more than 2× the target → +30%): $7.76 → $10.09; modifier 313%; daily read to 09-28</t>
+          <t>Push TOS +30% (3% of required top-of-search clicks delivered → +30%): $7.76 → $10.09; modifier 313%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $6.29 → $7.86; modifier 191%; daily read to 09-28</t>
+          <t>Push TOS +30% (25% of required top-of-search clicks delivered → +30%): $6.29 → $8.18; modifier 203%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $2.90 → $3.62; modifier 126%; re-point the ad to the serving child; daily read to 09-28</t>
+          <t>Push TOS +10% (no click requirement on file → +20% (a stated departure: the logic document would hold at the ceiling); halved — impression share did not rise after the 15 Sep raise (0.0% → 0.0%)): $2.90 → $3.19; modifier 99%; re-point the ad to the serving child; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 32 vs target 9: more than 2× the target → +30%): $4.87 → $6.33; modifier 339%; daily read to 09-28</t>
+          <t>Push TOS +30% (15% of required top-of-search clicks delivered → +30%): $4.87 → $6.33; modifier 339%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 13 vs target 6: more than 2× the target → +30%): $6.62 → $8.61; modifier 339%; daily read to 09-28</t>
+          <t>Push TOS +30% (15% of required top-of-search clicks delivered → +30%): $6.62 → $8.61; modifier 339%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 57 vs target 9: more than 2× the target → +30%): $4.79 → $6.23; modifier 297%; daily read to 09-28</t>
+          <t>Push TOS +30% (19% of required top-of-search clicks delivered → +30%): $4.79 → $6.23; modifier 297%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Push TOS +10% (rank 2 vs target 1: within 5 positions → +10%): $4.79 → $5.27; modifier 236%; daily read to 09-28</t>
+          <t>Push TOS +30% (2% of required top-of-search clicks delivered → +30%): $4.79 → $6.23; modifier 297%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>41 → 28 → 1</t>
+          <t>29 → 27 → 1</t>
         </is>
       </c>
       <c r="M28" t="n">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 28 vs target 1: more than 2× the target → +30%): $5.08 → $6.61; modifier 341%; daily read to 09-28</t>
+          <t>Push TOS +30% (3% of required top-of-search clicks delivered → +30%): $5.08 → $6.61; modifier 341%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 24 vs target 1: more than 2× the target → +30%): $5.32 → $6.92; modifier 341%; daily read to 09-28</t>
+          <t>Push TOS +30% (12% of required top-of-search clicks delivered → +30%): $5.32 → $6.92; modifier 341%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $7.80 → $9.75; modifier 225%; daily read to 09-28</t>
+          <t>Push TOS +20% (no click requirement on file → +20% (a stated departure: the logic document would hold at the ceiling)): $7.80 → $9.36; modifier 212%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $6.42 → $8.02; modifier 204%; daily read to 09-28</t>
+          <t>Push TOS +20% (no click requirement on file → +20% (a stated departure: the logic document would hold at the ceiling)): $6.42 → $7.70; modifier 192%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>32 → 24 → 8</t>
+          <t>19 → 25 → 8</t>
         </is>
       </c>
       <c r="M32" t="n">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 24 vs target 8: more than 2× the target → +30%): $6.41 → $8.33; modifier 343%; budget $35.00 → $45.50; daily read to 09-28</t>
+          <t>Push TOS +30% (10% of required top-of-search clicks delivered → +30%): $6.41 → $8.33; modifier 343%; budget $35.00 → $45.50; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $5.43 → $6.78; modifier 198%; daily read to 09-28</t>
+          <t>Push TOS +10% (no click requirement on file → +20% (a stated departure: the logic document would hold at the ceiling); halved — impression share did not rise after the 15 Sep raise (7.6% → 5.0%)): $5.43 → $5.97; modifier 162%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 12 vs target 1: more than 2× the target → +30%): $5.48 → $7.13; modifier 385%; daily read to 09-28</t>
+          <t>Push TOS +15% (4% of required top-of-search clicks delivered → +30%; halved — impression share did not rise after the 15 Sep raise (5.9% → 3.8%)): $5.48 → $6.31; modifier 329%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>40 → 49 → 6</t>
+          <t>37 → 46 → 6</t>
         </is>
       </c>
       <c r="M35" t="n">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Switch to fixed bidding; Push TOS +30% (rank 49 vs target 6: more than 2× the target → +30%): $6.69 → $8.70; modifier 365%; budget $49.72 → $64.64; re-point the ad to the serving child; daily read to 09-28</t>
+          <t>Switch to fixed bidding; Push TOS +30% (11% of required top-of-search clicks delivered → +30%; fixed bidding starts near what dynamic paid in the deal (11.99)): $6.69 → $11.99; modifier 541%; budget $49.72 → $64.64; re-point the ad to the serving child; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>45 → 24 → 10</t>
+          <t>29 → 33 → 10</t>
         </is>
       </c>
       <c r="M36" t="n">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 24 vs target 10: more than 2× the target → +30%): $7.42 → $9.65; modifier 419%; budget $272.36 → $354.07; daily read to 09-28</t>
+          <t>Push TOS +30% (26% of required top-of-search clicks delivered → +30%): $7.42 → $9.65; modifier 419%; budget $272.36 → $354.07; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>32 → 36 → 1</t>
+          <t>36 → 45 → 1</t>
         </is>
       </c>
       <c r="M37" t="n">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 36 vs target 1: more than 2× the target → +30%): $3.53 → $4.59; modifier 282%; daily read to 09-28</t>
+          <t>Push TOS +30% (2% of required top-of-search clicks delivered → +30%): $3.53 → $4.59; modifier 282%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $4.04 → $5.05; modifier 126%; daily read to 09-28</t>
+          <t>Push TOS +20% (no click requirement on file → +20% (a stated departure: the logic document would hold at the ceiling)): $4.04 → $4.84; modifier 117%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $5.95 → $7.43; modifier 291%; daily read to 09-28</t>
+          <t>Push TOS +20% (no click requirement on file → +20% (a stated departure: the logic document would hold at the ceiling)): $5.95 → $7.14; modifier 276%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 50 vs target 7: more than 2× the target → +30%): $3.51 → $4.56; modifier 251%; daily read to 09-28</t>
+          <t>Push TOS +30% (12% of required top-of-search clicks delivered → +30%): $3.51 → $4.56; modifier 251%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $5.45 → $6.82; modifier 259%; daily read to 09-28</t>
+          <t>Push TOS +15% (5% of required top-of-search clicks delivered → +30%; halved — impression share did not rise after the 15 Sep raise (5.0% → 0.1%)): $5.45 → $6.27; modifier 230%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 20 vs target 2: more than 2× the target → +30%): $5.78 → $7.51; modifier 400%; daily read to 09-28</t>
+          <t>Push TOS +30% (0% of required top-of-search clicks delivered → +30%): $5.78 → $7.51; modifier 400%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 23 vs target 2: more than 2× the target → +30%): $5.12 → $6.65; modifier 343%; daily read to 09-28</t>
+          <t>Push TOS +30% (9% of required top-of-search clicks delivered → +30%): $5.12 → $6.65; modifier 343%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $6.31 → $7.88; modifier 265%; daily read to 09-28</t>
+          <t>Push TOS +10% (no click requirement on file → +20% (a stated departure: the logic document would hold at the ceiling); halved — impression share did not rise after the 15 Sep raise (5.0% → 4.3%)): $6.31 → $6.94; modifier 221%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 49 vs target 7: more than 2× the target → +30%): $3.90 → $5.08; modifier 217%; daily read to 09-28</t>
+          <t>Push TOS +30% (0% of required top-of-search clicks delivered → +30%): $3.90 → $5.08; modifier 217%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -3540,7 +3540,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 80 vs target 2: more than 2× the target → +30%): $4.94 → $6.42; modifier 221%; daily read to 09-28</t>
+          <t>Push TOS +30% (29% of required top-of-search clicks delivered → +30%): $4.94 → $6.42; modifier 221%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -3607,7 +3607,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $5.37 → $6.71; modifier 124%; daily read to 09-28</t>
+          <t>Push TOS +30% (10% of required top-of-search clicks delivered → +30%): $5.37 → $6.98; modifier 133%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $4.94 → $6.17; modifier 209%; daily read to 09-28</t>
+          <t>Push TOS +20% (no click requirement on file → +20% (a stated departure: the logic document would hold at the ceiling)): $4.94 → $5.93; modifier 196%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 55 vs target 13: more than 2× the target → +30%): $3.20 → $4.16; modifier 160%; daily read to 09-28</t>
+          <t>Push TOS +30% (10% of required top-of-search clicks delivered → +30%): $3.20 → $4.16; modifier 160%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $3.46 → $4.32; modifier 138%; daily read to 09-28</t>
+          <t>Push TOS +20% (no click requirement on file → +20% (a stated departure: the logic document would hold at the ceiling)): $3.46 → $4.15; modifier 128%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 55 vs target 15: more than 2× the target → +30%): $3.68 → $4.78; modifier 403%; daily read to 09-28</t>
+          <t>Push TOS +30% (1% of required top-of-search clicks delivered → +30%): $3.68 → $4.78; modifier 403%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 34 vs target 1: more than 2× the target → +30%): $4.79 → $6.23; modifier 297%; daily read to 09-28</t>
+          <t>Push TOS +30% (27% of required top-of-search clicks delivered → +30%): $4.79 → $6.23; modifier 297%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 29 vs target 1: more than 2× the target → +30%): $4.75 → $6.17; modifier 225%; daily read to 09-28</t>
+          <t>Push TOS +15% (0% of required top-of-search clicks delivered → +30%; halved — impression share did not rise after the 15 Sep raise (8.4% → 2.7%)): $4.75 → $5.46; modifier 188%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $3.72 → $4.65; modifier 225%; daily read to 09-28</t>
+          <t>Push TOS +20% (no click requirement on file → +20% (a stated departure: the logic document would hold at the ceiling)): $3.72 → $4.46; modifier 212%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $4.80 → $6.00; modifier 100%; daily read to 09-28</t>
+          <t>Push TOS +20% (no click requirement on file → +20% (a stated departure: the logic document would hold at the ceiling)): $4.80 → $5.76; modifier 92%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 24 vs target 1: more than 2× the target → +30%): $4.98 → $6.47; modifier 312%; daily read to 09-28</t>
+          <t>Push TOS +30% (6% of required top-of-search clicks delivered → +30%): $4.98 → $6.47; modifier 312%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 40 vs target 1: more than 2× the target → +30%): $3.58 → $4.65; modifier 258%; daily read to 09-28</t>
+          <t>Push TOS +30% (0% of required top-of-search clicks delivered → +30%): $3.58 → $4.65; modifier 258%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 31 vs target 10: more than 2× the target → +30%): $6.42 → $8.35; modifier 432%; daily read to 09-28</t>
+          <t>Push TOS +30% (6% of required top-of-search clicks delivered → +30%): $6.42 → $8.35; modifier 432%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 30 vs target 9: more than 2× the target → +30%): $6.42 → $8.35; modifier 432%; daily read to 09-28</t>
+          <t>Push TOS +30% (8% of required top-of-search clicks delivered → +30%): $6.42 → $8.35; modifier 432%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 64 vs target 15: more than 2× the target → +30%): $5.87 → $7.63; modifier 161%; budget $5.00 → $6.50; daily read to 09-28</t>
+          <t>Push TOS +20% (66% of required top-of-search clicks delivered → +20%): $5.87 → $7.04; modifier 141%; budget $5.00 → $6.50; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -4484,12 +4484,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>King Sheets Cooling-[Cooling|King]-(MSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>King Cooling Sheets-[Cooling|King]-(MSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>IN · Bamboo|King</t>
+          <t>IN · Cooling|King</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4501,45 +4501,45 @@
         <v>5.18</v>
       </c>
       <c r="F61" t="n">
-        <v>25</v>
+        <v>252</v>
       </c>
       <c r="G61" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>53 → 48 → 12</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>17.97</v>
+        <v>13</v>
       </c>
       <c r="N61" t="n">
-        <v>0.19</v>
+        <v>1.06</v>
       </c>
       <c r="O61" t="n">
-        <v>9.76</v>
+        <v>5.93</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>budget $17.97→$23.36</t>
+          <t>budget $13→$16.9</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $9.76 → $12.20; modifier 412%; daily read to 09-28</t>
+          <t>Push TOS +10% (78% of required top-of-search clicks delivered → +10%): $5.93 → $6.52; modifier 443%; budget $13.00 → $16.90; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>King Sheets Deep Pocket Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>King Sheets Cooling-[Cooling|King]-(MSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4561,52 +4561,52 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>MSV</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6.47</v>
+        <v>5.18</v>
       </c>
       <c r="F62" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H62" t="n">
-        <v>0.059</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>27 → 33 → 1</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>10</v>
+        <v>17.97</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="O62" t="n">
-        <v>4.46</v>
+        <v>9.76</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>mod 135→194%; TOS $4.46→$5.59</t>
+          <t>budget $17.97→$23.36</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 33 vs target 1: more than 2× the target → +30%): $4.46 → $5.80; modifier 206%; daily read to 09-28</t>
+          <t>Push TOS +30% (30% of required top-of-search clicks delivered → +30%; stopped at the loss stop 12.63): $9.76 → $12.63; modifier 430%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>King Size Bamboo Sheets-[Bamboo|King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>King Sheets Deep Pocket Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4628,52 +4628,52 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E63" t="n">
         <v>6.47</v>
       </c>
       <c r="F63" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G63" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>21 → 28 → 11</t>
+          <t>27 → 33 → 1</t>
         </is>
       </c>
       <c r="M63" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="N63" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>6.6</v>
+        <v>4.46</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>holds</t>
+          <t>mod 135→194%; TOS $4.46→$5.59</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 28 vs target 11: more than 2× the target → +30%): $6.60 → $8.58; modifier 472%; daily read to 09-28</t>
+          <t>Push TOS +15% (0% of required top-of-search clicks delivered → +30%; halved — impression share did not rise after the 15 Sep raise (0.4% → 0.0%)): $4.46 → $5.13; modifier 170%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>King Size Bed Sheets Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>King Size Bamboo Sheets-[Bamboo|King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4695,17 +4695,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E64" t="n">
         <v>6.47</v>
       </c>
       <c r="F64" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -4714,33 +4714,33 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>26 → 23 → 8</t>
+          <t>21 → 28 → 11</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="N64" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="O64" t="n">
-        <v>6.17</v>
+        <v>6.6</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>mod 225→241%; TOS $6.17→$6.48</t>
+          <t>holds</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 23 vs target 8: more than 2× the target → +30%): $6.17 → $8.03; modifier 323%; daily read to 09-28</t>
+          <t>Push TOS +10% (88% of required top-of-search clicks delivered → +10%): $6.60 → $7.26; modifier 384%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -4752,12 +4752,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>King Size Cooling Bed Sheets-[Cooling|King]-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>King Size Bed Sheets Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>IN · Cooling|King</t>
+          <t>IN · Bamboo|King</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4766,14 +4766,14 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5.18</v>
+        <v>6.47</v>
       </c>
       <c r="F65" t="n">
+        <v>8</v>
+      </c>
+      <c r="G65" t="n">
         <v>1</v>
       </c>
-      <c r="G65" t="n">
-        <v>0</v>
-      </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
@@ -4781,30 +4781,33 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>— → 70 → 6</t>
+          <t>26 → 23 → 8</t>
         </is>
       </c>
       <c r="M65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>0.18</v>
+      </c>
+      <c r="O65" t="n">
+        <v>6.17</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>mod 100→367%</t>
+          <t>mod 225→241%; TOS $6.17→$6.48</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 70 vs target 6: more than 2× the target → +30%): — → —; daily read to 09-28</t>
+          <t>Push TOS +15% (5% of required top-of-search clicks delivered → +30%; halved — impression share did not rise after the 15 Sep raise (4.8% → 4.0%)): $6.17 → $7.10; modifier 274%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4819,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>King Size Cooling Sheet Set-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>King Size Cooling Bed Sheets-[Cooling|King]-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4833,11 +4836,14 @@
         <v>5.18</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -4849,7 +4855,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>— → 70 → 6</t>
         </is>
       </c>
       <c r="M66" t="n">
@@ -4860,12 +4866,12 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>holds</t>
+          <t>mod 100→367%</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): — → —; daily read to 09-28</t>
+          <t>Push TOS +30% (0% of required top-of-search clicks delivered → +30%): — → —; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4883,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>King Size Cooling Sheets Deep Pocket Set-[Cooling|King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>King Size Cooling Sheet Set-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4887,23 +4893,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E67" t="n">
         <v>5.18</v>
       </c>
       <c r="F67" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
-      <c r="H67" t="n">
-        <v>0.25</v>
-      </c>
       <c r="I67" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -4913,7 +4916,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>— → 61 → 3</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M67" t="n">
@@ -4922,17 +4925,14 @@
       <c r="N67" t="n">
         <v>0</v>
       </c>
-      <c r="O67" t="n">
-        <v>4.69</v>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>mod 147→172%; TOS $4.69→$5.17</t>
+          <t>holds</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 61 vs target 3: more than 2× the target → +30%): $4.69 → $6.10; modifier 221%; daily read to 09-28</t>
+          <t>Push TOS +30% (0% of required top-of-search clicks delivered → +30%): — → —; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -4944,62 +4944,62 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>King Size Sheets Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>King Size Cooling Sheets Deep Pocket Set-[Cooling|King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>IN · Bamboo|King</t>
+          <t>IN · Cooling|King</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6.47</v>
+        <v>5.18</v>
       </c>
       <c r="F68" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G68" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J68" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>37 → 19 → 9</t>
+          <t>— → 61 → 3</t>
         </is>
       </c>
       <c r="M68" t="n">
         <v>10</v>
       </c>
       <c r="N68" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>6.42</v>
+        <v>4.69</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>holds</t>
+          <t>mod 147→172%; TOS $4.69→$5.17</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 19 vs target 9: more than 2× the target → +30%): $6.42 → $8.35; modifier 456%; daily read to 09-28</t>
+          <t>Push TOS +15% (0% of required top-of-search clicks delivered → +30%; halved — impression share did not rise after the 15 Sep raise (10.3% → 9.2%)): $4.69 → $5.40; modifier 184%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>King Size Sheets Deep Pocket Set Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>King Size Sheets Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5028,10 +5028,10 @@
         <v>6.47</v>
       </c>
       <c r="F69" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -5040,33 +5040,33 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>37 → 19 → 9</t>
         </is>
       </c>
       <c r="M69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="O69" t="n">
-        <v>3.32</v>
+        <v>6.42</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>mod 75→119%; TOS $3.32→$4.16</t>
+          <t>holds</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $3.32 → $4.16; modifier 119%; daily read to 09-28</t>
+          <t>Push TOS +20% (58% of required top-of-search clicks delivered → +20%): $6.42 → $7.70; modifier 414%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>King Size Sheets Set Bamboo-[Bamboo|King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>King Size Sheets Deep Pocket Set Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5088,23 +5088,23 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E70" t="n">
         <v>6.47</v>
       </c>
       <c r="F70" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>31 → 29 → 10</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M70" t="n">
@@ -5124,16 +5124,16 @@
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>4.92</v>
+        <v>3.32</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>mod 224→239%; TOS $4.92→$5.15</t>
+          <t>mod 75→119%; TOS $3.32→$4.16</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 29 vs target 10: more than 2× the target → +30%): $4.92 → $6.40; modifier 321%; daily read to 09-28</t>
+          <t>Push TOS +20% (no click requirement on file → +20% (a stated departure: the logic document would hold at the ceiling)): $3.32 → $3.99; modifier 110%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -5145,30 +5145,33 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>King Size Sheets Set Cooling-[Cooling|King]-(MSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>King Size Sheets Set Bamboo-[Bamboo|King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>IN · Cooling|King</t>
+          <t>IN · Bamboo|King</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>MSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5.18</v>
+        <v>6.47</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
+      <c r="H71" t="n">
+        <v>0.07000000000000001</v>
+      </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5178,26 +5181,26 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>— → 45 → —</t>
+          <t>31 → 29 → 10</t>
         </is>
       </c>
       <c r="M71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N71" t="n">
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>3.71</v>
+        <v>4.92</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>mod 93→150%; TOS $3.71→$4.80</t>
+          <t>mod 224→239%; TOS $4.92→$5.15</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $3.71 → $4.63; modifier 141%; daily read to 09-28</t>
+          <t>Push TOS +15% (0% of required top-of-search clicks delivered → +30%; halved — impression share did not rise after the 15 Sep raise (2.5% → 0.5%)): $4.92 → $5.66; modifier 273%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -5209,62 +5212,59 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>King Size Sheets With Deep Pockets Bamboo-(NOSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>King Size Sheets Set Cooling-[Cooling|King]-(MSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>IN · Bamboo|King</t>
+          <t>IN · Cooling|King</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NOSV</t>
+          <t>MSV</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6.47</v>
+        <v>5.18</v>
       </c>
       <c r="F72" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>9</v>
-      </c>
-      <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>— → 45 → —</t>
         </is>
       </c>
       <c r="M72" t="n">
         <v>10</v>
       </c>
       <c r="N72" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>10.41</v>
+        <v>3.71</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>holds</t>
+          <t>mod 93→150%; TOS $3.71→$4.80</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $10.41 → $13.01; modifier 334%; daily read to 09-28</t>
+          <t>Push TOS +30% (0% of required top-of-search clicks delivered → +30%): $3.71 → $4.82; modifier 151%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Organic Bamboo Sheets King-[Bamboo|King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>King Size Sheets With Deep Pockets Bamboo-(NOSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5286,43 +5286,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>NOSV</t>
         </is>
       </c>
       <c r="E73" t="n">
         <v>6.47</v>
       </c>
       <c r="F73" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G73" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H73" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J73" t="n">
         <v>0.5</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>44 → 43 → 6</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M73" t="n">
-        <v>11.01</v>
+        <v>10</v>
       </c>
       <c r="N73" t="n">
-        <v>0.4</v>
+        <v>0.29</v>
       </c>
       <c r="O73" t="n">
-        <v>8.27</v>
+        <v>10.41</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 43 vs target 6: more than 2× the target → +30%): $8.27 → $10.75; modifier 449%; daily read to 09-28</t>
+          <t>Push TOS +20% (31% of required top-of-search clicks delivered → +20%): $10.41 → $12.49; modifier 316%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -5343,12 +5343,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Organic Bamboo Sheets-[Bamboo]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
+          <t>Organic Bamboo Sheets King-[Bamboo|King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>IN · Bamboo</t>
+          <t>IN · Bamboo|King</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5357,48 +5357,48 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6.32</v>
+        <v>6.47</v>
       </c>
       <c r="F74" t="n">
         <v>4</v>
       </c>
       <c r="G74" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>26 → 24 → 5</t>
+          <t>44 → 43 → 6</t>
         </is>
       </c>
       <c r="M74" t="n">
-        <v>31</v>
+        <v>11.01</v>
       </c>
       <c r="N74" t="n">
-        <v>0.02</v>
+        <v>0.4</v>
       </c>
       <c r="O74" t="n">
-        <v>4.41</v>
+        <v>8.27</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>mod 234→318%; TOS $4.41→$5.52</t>
+          <t>holds</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 24 vs target 5: more than 2× the target → +30%): $4.41 → $5.73; modifier 334%; re-point the ad to the serving child; daily read to 09-28</t>
+          <t>Push TOS +30% (12% of required top-of-search clicks delivered → +30%): $8.27 → $10.75; modifier 449%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -5410,62 +5410,62 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Queen Bed Sheet Set Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-TAUPE</t>
+          <t>Organic Bamboo Sheets-[Bamboo]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>IN · Bamboo|Queen</t>
+          <t>IN · Bamboo</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6.39</v>
+        <v>6.32</v>
       </c>
       <c r="F75" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H75" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>26 → 24 → 5</t>
         </is>
       </c>
       <c r="M75" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="O75" t="n">
-        <v>4.75</v>
+        <v>4.41</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>mod 150→213%; TOS $4.75→$5.95</t>
+          <t>mod 234→318%; TOS $4.41→$5.52</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $4.75 → $5.94; modifier 212%; daily read to 09-28</t>
+          <t>Push TOS +30% (9% of required top-of-search clicks delivered → +30%): $4.41 → $5.73; modifier 334%; re-point the ad to the serving child; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -5477,7 +5477,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Queen Deep Pocket Bamboo Sheets-[Bamboo|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
+          <t>Queen Bed Sheet Set Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-TAUPE</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5487,17 +5487,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E76" t="n">
         <v>6.39</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.2</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
@@ -5510,26 +5513,26 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>— → 45 → 1</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N76" t="n">
         <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>5.07</v>
+        <v>4.75</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>mod 238→322%; TOS $5.07→$6.33</t>
+          <t>mod 150→213%; TOS $4.75→$5.95</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 45 vs target 1: more than 2× the target → +30%): $5.07 → $6.59; modifier 339%; daily read to 09-28</t>
+          <t>Push TOS +20% (no click requirement on file → +20% (a stated departure: the logic document would hold at the ceiling)): $4.75 → $5.70; modifier 200%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5544,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Queen Sheet Set Bamboo-[Bamboo|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
+          <t>Queen Deep Pocket Bamboo Sheets-[Bamboo|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5558,13 +5561,10 @@
         <v>6.39</v>
       </c>
       <c r="F77" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>7</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0.763</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
@@ -5573,30 +5573,30 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>— → 46 → 6</t>
+          <t>— → 45 → 1</t>
         </is>
       </c>
       <c r="M77" t="n">
-        <v>10.71</v>
+        <v>10</v>
       </c>
       <c r="N77" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>4.99</v>
+        <v>5.07</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>mod 122→181%; TOS $4.99→$6.32</t>
+          <t>mod 238→322%; TOS $5.07→$6.33</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 46 vs target 6: more than 2× the target → +30%): $4.99 → $6.49; modifier 189%; re-point the ad to the serving child; daily read to 09-28</t>
+          <t>Push TOS +30% (0% of required top-of-search clicks delivered → +30%): $5.07 → $6.59; modifier 339%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Queen Size Bamboo Sheets Set-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-TAUPE</t>
+          <t>Queen Sheet Set Bamboo-[Bamboo|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5625,13 +5625,13 @@
         <v>6.39</v>
       </c>
       <c r="F78" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H78" t="n">
-        <v>0.439</v>
+        <v>0.763</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
@@ -5640,30 +5640,30 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>— → 49 → 4</t>
+          <t>— → 46 → 6</t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>30</v>
+        <v>10.71</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="O78" t="n">
-        <v>4.71</v>
+        <v>4.99</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>mod 174→243%; TOS $4.71→$5.90</t>
+          <t>mod 122→181%; TOS $4.99→$6.32</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 49 vs target 4: more than 2× the target → +30%): $4.71 → $6.13; modifier 256%; daily read to 09-28</t>
+          <t>Push TOS +15% (0% of required top-of-search clicks delivered → +30%; halved — impression share did not rise after the 15 Sep raise (0.5% → 0.4%)): $4.99 → $5.74; modifier 155%; re-point the ad to the serving child; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Queen Size Bamboo Sheets-[Bamboo|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
+          <t>Queen Size Bamboo Sheets Set-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-TAUPE</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5692,13 +5692,13 @@
         <v>6.39</v>
       </c>
       <c r="F79" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>0.439</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
@@ -5711,26 +5711,26 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>— → 53 → 4</t>
+          <t>— → 49 → 4</t>
         </is>
       </c>
       <c r="M79" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="N79" t="n">
         <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>1.52</v>
+        <v>4.71</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>mod 238→338%; TOS $1.52→$1.97</t>
+          <t>mod 174→243%; TOS $4.71→$5.90</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 53 vs target 4: more than 2× the target → +30%): $1.52 → $1.98; modifier 339%; daily read to 09-28</t>
+          <t>Push TOS +15% (0% of required top-of-search clicks delivered → +30%; halved — impression share did not rise after the 15 Sep raise (0.7% → 0.0%)): $4.71 → $5.42; modifier 215%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -5742,27 +5742,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Sheet Set Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Queen Size Bamboo Sheets-[Bamboo|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>IN · Bamboo</t>
+          <t>IN · Bamboo|Queen</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6.32</v>
+        <v>6.39</v>
       </c>
       <c r="F80" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>— → 53 → 4</t>
         </is>
       </c>
       <c r="M80" t="n">
@@ -5788,16 +5788,16 @@
         <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>5.88</v>
+        <v>1.52</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>mod 194→216%; TOS $5.88→$6.32</t>
+          <t>mod 238→338%; TOS $1.52→$1.97</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $5.88 → $7.35; modifier 268%; daily read to 09-28</t>
+          <t>Push TOS +30% (0% of required top-of-search clicks delivered → +30%): $1.52 → $1.98; modifier 339%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Sheets For Queen Size Bed Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
+          <t>Sheet Set Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>IN · Bamboo|Queen</t>
+          <t>IN · Bamboo</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5823,12 +5823,15 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6.39</v>
+        <v>6.32</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
@@ -5852,16 +5855,16 @@
         <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>2.86</v>
+        <v>5.88</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>holds</t>
+          <t>mod 194→216%; TOS $5.88→$6.32</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $2.86 → $3.58; modifier 225%; re-point the ad to the serving child; daily read to 09-28</t>
+          <t>Push TOS +20% (no click requirement on file → +20% (a stated departure: the logic document would hold at the ceiling)): $5.88 → $7.06; modifier 253%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -5873,12 +5876,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Sheets King Size Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Sheets For Queen Size Bed Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>IN · Bamboo|King</t>
+          <t>IN · Bamboo|Queen</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5887,16 +5890,13 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6.47</v>
+        <v>6.39</v>
       </c>
       <c r="F82" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0.167</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
@@ -5919,16 +5919,16 @@
         <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>mod 56→95%; TOS $2.96→$3.70</t>
+          <t>holds</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $2.96 → $3.71; modifier 95%; daily read to 09-28</t>
+          <t>Push TOS +30% (0% of required top-of-search clicks delivered → +30%): $2.86 → $3.72; modifier 238%; re-point the ad to the serving child; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Soft Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Sheets King Size Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>IN · Bamboo</t>
+          <t>IN · Bamboo|King</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6.32</v>
+        <v>6.47</v>
       </c>
       <c r="F83" t="n">
         <v>6</v>
@@ -5963,7 +5963,7 @@
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>0.333</v>
+        <v>0.167</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
@@ -5980,22 +5980,22 @@
         </is>
       </c>
       <c r="M83" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="N83" t="n">
         <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>4.52</v>
+        <v>2.96</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>mod 138→197%; TOS $4.52→$5.64</t>
+          <t>mod 56→95%; TOS $2.96→$3.70</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $4.52 → $5.65; modifier 197%; daily read to 09-28</t>
+          <t>Push TOS +20% (no click requirement on file → +20% (a stated departure: the logic document would hold at the ceiling)): $2.96 → $3.56; modifier 87%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Top Rated Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Soft Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6030,10 +6030,10 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>0.167</v>
+        <v>0.333</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="M84" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="N84" t="n">
         <v>0</v>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>Push TOS +25% (no rank read on file → +25%): $4.52 → $5.65; modifier 197%; daily read to 09-28</t>
+          <t>Push TOS +20% (no click requirement on file → +20% (a stated departure: the logic document would hold at the ceiling)): $4.52 → $5.43; modifier 186%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -6074,12 +6074,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>White Bamboo Sheets King-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Top Rated Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>IN · Bamboo|King</t>
+          <t>IN · Bamboo</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -6088,19 +6088,19 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6.47</v>
+        <v>6.32</v>
       </c>
       <c r="F85" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>0.333</v>
+        <v>0.167</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>11 → 10 → 4</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M85" t="n">
@@ -6120,16 +6120,16 @@
         <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>4.67</v>
+        <v>4.52</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>mod 146→207%; TOS $4.67→$5.83</t>
+          <t>mod 138→197%; TOS $4.52→$5.64</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 10 vs target 4: more than 2× the target → +30%): $4.67 → $6.08; modifier 220%; daily read to 09-28</t>
+          <t>Push TOS +20% (no click requirement on file → +20% (a stated departure: the logic document would hold at the ceiling)): $4.52 → $5.43; modifier 186%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -6141,12 +6141,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>White Bamboo Sheets Queen-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
+          <t>White Bamboo Sheets King-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>IN · Bamboo|Queen</t>
+          <t>IN · Bamboo|King</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -6155,16 +6155,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6.39</v>
+        <v>6.47</v>
       </c>
       <c r="F86" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>0.538</v>
+        <v>0.333</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
@@ -6177,7 +6177,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>— → 11 → 2</t>
+          <t>11 → 10 → 4</t>
         </is>
       </c>
       <c r="M86" t="n">
@@ -6187,16 +6187,16 @@
         <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>4</v>
+        <v>4.67</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>mod 134→192%; TOS $4.00→$4.99</t>
+          <t>mod 146→207%; TOS $4.67→$5.83</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 11 vs target 2: more than 2× the target → +30%): $4.00 → $5.20; modifier 204%; re-point the ad to the serving child; daily read to 09-28</t>
+          <t>Push TOS +30% (0% of required top-of-search clicks delivered → +30%): $4.67 → $6.08; modifier 220%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>White Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>White Bamboo Sheets Queen-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>IN · Bamboo</t>
+          <t>IN · Bamboo|Queen</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -6222,16 +6222,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6.32</v>
+        <v>6.39</v>
       </c>
       <c r="F87" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>0.375</v>
+        <v>0.538</v>
       </c>
       <c r="I87" t="n">
         <v>0</v>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>24 → 32 → 9</t>
+          <t>— → 11 → 2</t>
         </is>
       </c>
       <c r="M87" t="n">
@@ -6254,83 +6254,83 @@
         <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>3.57</v>
+        <v>4</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>mod 88→144%; TOS $3.57→$4.64</t>
+          <t>mod 134→192%; TOS $4.00→$4.99</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>Push TOS +30% (rank 32 vs target 9: more than 2× the target → +30%): $3.57 → $4.64; modifier 144%; daily read to 09-28</t>
+          <t>Push TOS +15% (0% of required top-of-search clicks delivered → +30%; halved — impression share did not rise after the 15 Sep raise (0.0% → 0.0%)): $4.00 → $4.60; modifier 169%; re-point the ad to the serving child; daily read to 09-28</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A · In focus — restore + push</t>
+          <t>A · In focus — push top of search</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Bamboo Sheets King Size-(HSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>White Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>IN · Bamboo|King</t>
+          <t>IN · Bamboo</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>HSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6.47</v>
+        <v>6.32</v>
       </c>
       <c r="F88" t="n">
-        <v>905</v>
+        <v>24</v>
       </c>
       <c r="G88" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="I88" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>30 → 20 → 10</t>
+          <t>24 → 32 → 9</t>
         </is>
       </c>
       <c r="M88" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="N88" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>4.96</v>
+        <v>3.57</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>mod 210→296%; base ↓22%; TOS $4.96→$4.95</t>
+          <t>mod 88→144%; TOS $3.57→$4.64</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>Restore pre-cut prices, then push TOS +20% (rank 20 vs target 10: up to 2× the target → +20%): $4.96 → $5.95; base −25% for product pages at 50% (d14): base $1.60 → $1.20; modifier 396%; daily read to 09-28</t>
+          <t>Push TOS +30% (0% of required top-of-search clicks delivered → +30%): $3.57 → $4.64; modifier 144%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -6342,62 +6342,62 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>King Sheets Cooling-(MSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Bamboo Sheets King Size-(HSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>IN · Cooling|King</t>
+          <t>IN · Bamboo|King</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>MSV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5.18</v>
+        <v>6.47</v>
       </c>
       <c r="F89" t="n">
-        <v>105</v>
+        <v>905</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H89" t="n">
-        <v>0.171</v>
+        <v>0.5</v>
       </c>
       <c r="I89" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>— → 20 → 6</t>
+          <t>21 → 21 → 10</t>
         </is>
       </c>
       <c r="M89" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="N89" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="O89" t="n">
-        <v>2.85</v>
+        <v>4.96</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>budget $5→$9.64</t>
+          <t>mod 210→296%; base ↓22%; TOS $4.96→$4.95</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>Restore pre-cut prices, then push TOS +30% (rank 20 vs target 6: more than 2× the target → +30%): $2.85 → $3.70; modifier 95%; daily read to 09-28</t>
+          <t>Restore pre-cut prices, then push TOS +30% (1% of required top-of-search clicks delivered → +30%): $4.96 → $6.45; base −25% for product pages at 50% (d14): base $1.60 → $1.20; modifier 437%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -6409,12 +6409,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Queen Bamboo Sheet Set-(MSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-TAUPE</t>
+          <t>King Sheets Cooling-(MSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>IN · Bamboo|Queen</t>
+          <t>IN · Cooling|King</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -6423,19 +6423,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6.39</v>
+        <v>5.18</v>
       </c>
       <c r="F90" t="n">
-        <v>162</v>
+        <v>105</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>0.796</v>
+        <v>0.171</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -6445,26 +6445,26 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>29 → 22 → 7</t>
+          <t>— → 20 → 6</t>
         </is>
       </c>
       <c r="M90" t="n">
-        <v>12.86</v>
+        <v>5</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="O90" t="n">
-        <v>3.8</v>
+        <v>2.85</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>mod 166→230%; TOS $3.80→$4.72</t>
+          <t>budget $5→$9.64</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>Restore pre-cut prices, then push TOS +30% (rank 22 vs target 7: more than 2× the target → +30%): $3.80 → $4.94; modifier 246%; daily read to 09-28</t>
+          <t>Restore pre-cut prices, then push TOS +30% (0% of required top-of-search clicks delivered → +30%): $2.85 → $3.70; modifier 95%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>— → — → 10</t>
+          <t>72 → 59 → 10</t>
         </is>
       </c>
       <c r="M91" t="n">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>— → 66 → 21</t>
+          <t>101 → 72 → 21</t>
         </is>
       </c>
       <c r="M93" t="n">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Cooling Fitted Sheet Full-(LSV)-Exact-(Ranking)-DO-BAMBOO-FULL-LIGHTBLUE</t>
+          <t>Bamboo Sheets Full Size-[Bamboo|Full]-(MSV)-Exact-(Ranking)-DO-BAMBOO-FULL-OLIVE</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6888,47 +6888,47 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>MSV</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5.18</v>
+        <v>7.22</v>
       </c>
       <c r="F97" t="n">
-        <v>11</v>
+        <v>188</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H97" t="n">
-        <v>0.091</v>
+        <v>0.186</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>81 → 128 → —</t>
+          <t>36 → 47 → 10</t>
         </is>
       </c>
       <c r="M97" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="O97" t="n">
-        <v>4.94</v>
+        <v>4.96</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>holds</t>
+          <t>mod 351→451%; base ↓10%; TOS $4.96→$5.45</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
@@ -6945,7 +6945,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cooling Sheets Full Size-[Cooling|Full]-(MSV)-Exact-(Ranking)-DO-BAMBOO-FULL-LIGHTBLUE</t>
+          <t>Bamboo Sheets Twin-(MSV)-Exact-(Ranking)-DO-BAMBOO-TWIN-WHITE</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6959,36 +6959,39 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6.19</v>
+        <v>6.47</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0.308</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>55 → 87 → 13</t>
+          <t>25 → 36 → 20</t>
         </is>
       </c>
       <c r="M98" t="n">
         <v>10</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="O98" t="n">
-        <v>2.03</v>
+        <v>3.86</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
@@ -7009,7 +7012,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Cooling Sheets Full Size-[Cooling|Full]-(MSV)-Exact-(Ranking)-DO-BAMBOO-FULL-OLIVE</t>
+          <t>Cooling Fitted Sheet Full-(LSV)-Exact-(Ranking)-DO-BAMBOO-FULL-LIGHTBLUE</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -7019,43 +7022,43 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>MSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6.19</v>
+        <v>5.18</v>
       </c>
       <c r="F99" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>81 → 128 → —</t>
+        </is>
+      </c>
+      <c r="M99" t="n">
         <v>5</v>
       </c>
-      <c r="H99" t="n">
-        <v>0.632</v>
-      </c>
-      <c r="I99" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J99" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>80 → 135 → —</t>
-        </is>
-      </c>
-      <c r="M99" t="n">
-        <v>10</v>
-      </c>
       <c r="N99" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>2.03</v>
+        <v>4.94</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
@@ -7076,7 +7079,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Full Bamboo Sheets-(LSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE</t>
+          <t>Cooling Sheets Full Size-[Cooling|Full]-(MSV)-Exact-(Ranking)-DO-BAMBOO-FULL-LIGHTBLUE</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7086,11 +7089,11 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>MSV</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6.47</v>
+        <v>6.19</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
@@ -7109,7 +7112,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>19 → 56 → —</t>
+          <t>55 → 87 → 13</t>
         </is>
       </c>
       <c r="M100" t="n">
@@ -7119,7 +7122,7 @@
         <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>2.91</v>
+        <v>2.03</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
@@ -7140,7 +7143,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Full Size Bed Sheets Cooling-[Cooling|Full]-(LSV)-Exact-(Ranking)-DO-BAMBOO-FULL-LIGHTBLUE</t>
+          <t>Cooling Sheets Full Size-[Cooling|Full]-(MSV)-Exact-(Ranking)-DO-BAMBOO-FULL-OLIVE</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7150,20 +7153,20 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>MSV</t>
         </is>
       </c>
       <c r="E101" t="n">
         <v>6.19</v>
       </c>
       <c r="F101" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H101" t="n">
-        <v>0.1</v>
+        <v>0.632</v>
       </c>
       <c r="I101" t="n">
         <v>0.2</v>
@@ -7176,17 +7179,17 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>81 → 122 → —</t>
+          <t>80 → 135 → —</t>
         </is>
       </c>
       <c r="M101" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="O101" t="n">
-        <v>4.81</v>
+        <v>2.03</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
@@ -7207,7 +7210,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Full Size Sheets Bamboo-[Bamboo|Full]-(LSV)-Exact-(Ranking)-DO-BAMBOO-FULL-OLIVE</t>
+          <t>Full Bamboo Sheets-(LSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -7221,39 +7224,36 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>7.22</v>
+        <v>6.47</v>
       </c>
       <c r="F102" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>16</v>
-      </c>
-      <c r="H102" t="n">
-        <v>0.312</v>
+        <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>30 → 65 → —</t>
+          <t>19 → 56 → —</t>
         </is>
       </c>
       <c r="M102" t="n">
         <v>10</v>
       </c>
       <c r="N102" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>8.74</v>
+        <v>2.91</v>
       </c>
       <c r="P102" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Full Size Sheets Cooling-[Cooling|Full]-(LSV)-Exact-(Ranking)-DO-BAMBOO-FULL-LIGHTBLUE</t>
+          <t>Full Size Bed Sheets Cooling-[Cooling|Full]-(LSV)-Exact-(Ranking)-DO-BAMBOO-FULL-LIGHTBLUE</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -7291,13 +7291,13 @@
         <v>6.19</v>
       </c>
       <c r="F103" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>0.207</v>
+        <v>0.1</v>
       </c>
       <c r="I103" t="n">
         <v>0.2</v>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>64 → 99 → —</t>
+          <t>81 → 122 → —</t>
         </is>
       </c>
       <c r="M103" t="n">
@@ -7320,7 +7320,7 @@
         <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>2.87</v>
+        <v>4.81</v>
       </c>
       <c r="P103" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Sheets Cooling-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Full Size Sheets Bamboo-[Bamboo|Full]-(LSV)-Exact-(Ranking)-DO-BAMBOO-FULL-OLIVE</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -7351,43 +7351,43 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5.18</v>
+        <v>7.22</v>
       </c>
       <c r="F104" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H104" t="n">
-        <v>0.059</v>
+        <v>0.312</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="K104" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>68 → 133 → —</t>
+          <t>30 → 65 → —</t>
         </is>
       </c>
       <c r="M104" t="n">
         <v>10</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="O104" t="n">
-        <v>3.71</v>
+        <v>8.74</v>
       </c>
       <c r="P104" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Sheets Queen Cooling-[Cooling|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
+          <t>Full Size Sheets Cooling-[Cooling|Full]-(LSV)-Exact-(Ranking)-DO-BAMBOO-FULL-LIGHTBLUE</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7425,16 +7425,16 @@
         <v>6.19</v>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>0.207</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -7444,17 +7444,17 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>32 → 90 → —</t>
+          <t>64 → 99 → —</t>
         </is>
       </c>
       <c r="M105" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N105" t="n">
         <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>4.94</v>
+        <v>2.87</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
@@ -7470,12 +7470,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>B · Out of focus, thin — hold</t>
+          <t>B · Out of focus, rank collapse — freeze</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Antimicrobial Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Sheets Cooling-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7489,19 +7489,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6.47</v>
+        <v>5.18</v>
       </c>
       <c r="F106" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="I106" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -7511,17 +7511,17 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>68 → 133 → —</t>
         </is>
       </c>
       <c r="M106" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N106" t="n">
         <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>3.59</v>
+        <v>3.71</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
@@ -7530,19 +7530,19 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>Hold flat — no cut, no raise</t>
+          <t>Freeze price and budget; investigate the rank loss</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>B · Out of focus, thin — hold</t>
+          <t>B · Out of focus, rank collapse — freeze</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Bamboo Bed Sheets Full-(VLSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE</t>
+          <t>Sheets Queen Cooling-[Cooling|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7552,43 +7552,43 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6.47</v>
+        <v>6.19</v>
       </c>
       <c r="F107" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G107" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>32 → 90 → —</t>
         </is>
       </c>
       <c r="M107" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N107" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>4.75</v>
+        <v>4.94</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>Hold flat — no cut, no raise</t>
+          <t>Freeze price and budget; investigate the rank loss</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Bamboo Bed Sheets King Size-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Antimicrobial Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7626,16 +7626,16 @@
         <v>6.47</v>
       </c>
       <c r="F108" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -7649,13 +7649,13 @@
         </is>
       </c>
       <c r="M108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N108" t="n">
         <v>0</v>
       </c>
       <c r="O108" t="n">
-        <v>2.34</v>
+        <v>3.59</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Bamboo Cal King Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-CALIFKING-WHITE</t>
+          <t>Bamboo Bed Sheets Full-(VLSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7693,16 +7693,16 @@
         <v>6.47</v>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G109" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J109" t="n">
         <v>0.1</v>
@@ -7719,10 +7719,10 @@
         <v>5</v>
       </c>
       <c r="N109" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="O109" t="n">
-        <v>3.71</v>
+        <v>4.75</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Bamboo California King Sheets-[Bamboo|California King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-CALIFKING-WHITE</t>
+          <t>Bamboo Bed Sheets King Size-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7753,26 +7753,26 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E110" t="n">
         <v>6.47</v>
       </c>
       <c r="F110" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="G110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>0.353</v>
+        <v>0</v>
       </c>
       <c r="I110" t="n">
         <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
@@ -7786,10 +7786,10 @@
         <v>10</v>
       </c>
       <c r="N110" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>4.8</v>
+        <v>2.34</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Bamboo Cooling Queen Sheets-[Bamboo|Cooling]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
+          <t>Bamboo Cal King Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-CALIFKING-WHITE</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7820,17 +7820,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5.68</v>
+        <v>6.47</v>
       </c>
       <c r="F111" t="n">
         <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -7839,10 +7839,10 @@
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -7850,10 +7850,13 @@
         </is>
       </c>
       <c r="M111" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>0.14</v>
+      </c>
+      <c r="O111" t="n">
+        <v>3.71</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
@@ -7874,7 +7877,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Bamboo Cooling Sheets King Size-[Bamboo|Cooling]-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Bamboo California King Sheets-[Bamboo|California King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-CALIFKING-WHITE</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7888,39 +7891,39 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5.68</v>
+        <v>6.47</v>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="G112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H112" t="n">
-        <v>0.333</v>
+        <v>0.353</v>
       </c>
       <c r="I112" t="n">
         <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>— → 12 → 7</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M112" t="n">
-        <v>11.42</v>
+        <v>10</v>
       </c>
       <c r="N112" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="O112" t="n">
-        <v>3.54</v>
+        <v>4.8</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
@@ -7941,7 +7944,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Bamboo Fitted Sheet Twin-(VLSV)-Exact-(Ranking)-DO-BAMBOO-TWIN-LIGHTBLUE</t>
+          <t>Bamboo Cooling Queen Sheets-[Bamboo|Cooling]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7951,20 +7954,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6.47</v>
+        <v>5.68</v>
       </c>
       <c r="F113" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="I113" t="n">
         <v>0</v>
@@ -7986,9 +7989,6 @@
       <c r="N113" t="n">
         <v>0</v>
       </c>
-      <c r="O113" t="n">
-        <v>4.69</v>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>holds</t>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Bamboo Fitted Sheet-(MSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Bamboo Cooling Sheets King Size-[Bamboo|Cooling]-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -8018,43 +8018,43 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>MSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6.47</v>
+        <v>5.68</v>
       </c>
       <c r="F114" t="n">
+        <v>3</v>
+      </c>
+      <c r="G114" t="n">
+        <v>3</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="n">
         <v>1</v>
       </c>
-      <c r="G114" t="n">
-        <v>1</v>
-      </c>
-      <c r="H114" t="n">
-        <v>0</v>
-      </c>
-      <c r="I114" t="n">
-        <v>0</v>
-      </c>
-      <c r="J114" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K114" t="n">
-        <v>0</v>
-      </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>— → — → 2</t>
+          <t>— → 12 → 7</t>
         </is>
       </c>
       <c r="M114" t="n">
-        <v>5</v>
+        <v>11.42</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="O114" t="n">
-        <v>4.08</v>
+        <v>3.54</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Bamboo Full Size Sheets-[Bamboo|Full]-(VLSV)-Exact-(Ranking)-DO-BAMBOO-FULL-OLIVE</t>
+          <t>Bamboo Fitted Sheet Twin-(VLSV)-Exact-(Ranking)-DO-BAMBOO-TWIN-LIGHTBLUE</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -8089,22 +8089,22 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>7.22</v>
+        <v>6.47</v>
       </c>
       <c r="F115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
@@ -8118,10 +8118,10 @@
         <v>10</v>
       </c>
       <c r="N115" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
-        <v>4.35</v>
+        <v>4.69</v>
       </c>
       <c r="P115" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Bamboo Green Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-SAGE GREEN</t>
+          <t>Bamboo Fitted Sheet-(MSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -8152,20 +8152,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>MSV</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6.39</v>
+        <v>6.47</v>
       </c>
       <c r="F116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G116" t="n">
         <v>1</v>
       </c>
       <c r="H116" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="I116" t="n">
         <v>0</v>
@@ -8178,17 +8178,17 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>— → — → 2</t>
         </is>
       </c>
       <c r="M116" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N116" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>4.94</v>
+        <v>4.08</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Bamboo King Fitted Sheet-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Bamboo Full Size Sheets-[Bamboo|Full]-(VLSV)-Exact-(Ranking)-DO-BAMBOO-FULL-OLIVE</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -8219,26 +8219,26 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6.47</v>
+        <v>7.22</v>
       </c>
       <c r="F117" t="n">
         <v>2</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
@@ -8249,13 +8249,13 @@
         </is>
       </c>
       <c r="M117" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="O117" t="n">
-        <v>5.56</v>
+        <v>4.35</v>
       </c>
       <c r="P117" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Bamboo Organic Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Bamboo Green Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-SAGE GREEN</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -8290,22 +8290,22 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6.47</v>
+        <v>6.39</v>
       </c>
       <c r="F118" t="n">
         <v>3</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H118" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
@@ -8319,7 +8319,7 @@
         <v>10</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="O118" t="n">
         <v>4.94</v>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Bamboo Queen Sheet Set Deep Pocket-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-TAUPE</t>
+          <t>Bamboo King Fitted Sheet-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -8353,11 +8353,11 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6.39</v>
+        <v>6.47</v>
       </c>
       <c r="F119" t="n">
         <v>2</v>
@@ -8369,7 +8369,7 @@
         <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -8383,13 +8383,13 @@
         </is>
       </c>
       <c r="M119" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="N119" t="n">
         <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>5.27</v>
+        <v>5.56</v>
       </c>
       <c r="P119" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Bamboo Sheet Set Full-(VLSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE</t>
+          <t>Bamboo Organic Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -8427,16 +8427,16 @@
         <v>6.47</v>
       </c>
       <c r="F120" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>0.231</v>
+        <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -8450,13 +8450,13 @@
         </is>
       </c>
       <c r="M120" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N120" t="n">
         <v>0</v>
       </c>
       <c r="O120" t="n">
-        <v>3.8</v>
+        <v>4.94</v>
       </c>
       <c r="P120" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Bamboo Sheets Cal King Deep Pocket-(VLSV)-Exact-(Ranking)-DO-BAMBOO-CALIFKING-WHITE</t>
+          <t>Bamboo Queen Sheet Set Deep Pocket-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-TAUPE</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -8491,25 +8491,25 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6.47</v>
+        <v>6.39</v>
       </c>
       <c r="F121" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G121" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -8517,13 +8517,13 @@
         </is>
       </c>
       <c r="M121" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N121" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>4.46</v>
+        <v>5.27</v>
       </c>
       <c r="P121" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Bamboo Sheets Cal King-(VLSV)-Exact-(Ranking)-DO-BAMBOO-CALIFKING-WHITE</t>
+          <t>Bamboo Sheet Set Full-(VLSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -8561,22 +8561,22 @@
         <v>6.47</v>
       </c>
       <c r="F122" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G122" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>0</v>
+        <v>0.231</v>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J122" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -8587,10 +8587,10 @@
         <v>5</v>
       </c>
       <c r="N122" t="n">
-        <v>0.49</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>5.71</v>
+        <v>3.8</v>
       </c>
       <c r="P122" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Bamboo Sheets California King-(LSV)-Exact-(Ranking)-DO-BAMBOO-CALIFKING-WHITE</t>
+          <t>Bamboo Sheets Cal King Deep Pocket-(VLSV)-Exact-(Ranking)-DO-BAMBOO-CALIFKING-WHITE</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8621,26 +8621,26 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E123" t="n">
         <v>6.47</v>
       </c>
       <c r="F123" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="G123" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H123" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="I123" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J123" t="n">
         <v>0.1</v>
-      </c>
-      <c r="J123" t="n">
-        <v>0.8</v>
       </c>
       <c r="K123" t="n">
         <v>1</v>
@@ -8654,10 +8654,10 @@
         <v>10</v>
       </c>
       <c r="N123" t="n">
-        <v>0.33</v>
+        <v>0.05</v>
       </c>
       <c r="O123" t="n">
-        <v>4.6</v>
+        <v>4.46</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Bamboo Sheets Full Size Bed Set-(VLSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE</t>
+          <t>Bamboo Sheets Cal King-(VLSV)-Exact-(Ranking)-DO-BAMBOO-CALIFKING-WHITE</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8695,22 +8695,22 @@
         <v>6.47</v>
       </c>
       <c r="F124" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G124" t="n">
+        <v>4</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K124" t="n">
         <v>2</v>
-      </c>
-      <c r="H124" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="I124" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J124" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K124" t="n">
-        <v>0</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -8721,10 +8721,10 @@
         <v>5</v>
       </c>
       <c r="N124" t="n">
-        <v>0.25</v>
+        <v>0.49</v>
       </c>
       <c r="O124" t="n">
-        <v>6.17</v>
+        <v>5.71</v>
       </c>
       <c r="P124" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Bamboo Sheets Olive-(VHSV)-Exact-(Ranking)-DO-BAMBOO-KING-OLIVE</t>
+          <t>Bamboo Sheets California King-(LSV)-Exact-(Ranking)-DO-BAMBOO-CALIFKING-WHITE</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8755,29 +8755,29 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VHSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E125" t="n">
         <v>6.47</v>
       </c>
       <c r="F125" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H125" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J125" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="K125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L125" t="inlineStr">
         <is>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="M125" t="n">
-        <v>7.33</v>
+        <v>10</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="O125" t="n">
-        <v>3.59</v>
+        <v>4.6</v>
       </c>
       <c r="P125" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Bamboo Sheets Organic-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Bamboo Sheets Full Size Bed Set-(VLSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8829,19 +8829,19 @@
         <v>6.47</v>
       </c>
       <c r="F126" t="n">
+        <v>6</v>
+      </c>
+      <c r="G126" t="n">
         <v>2</v>
       </c>
-      <c r="G126" t="n">
-        <v>0</v>
-      </c>
       <c r="H126" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K126" t="n">
         <v>0</v>
@@ -8852,13 +8852,13 @@
         </is>
       </c>
       <c r="M126" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="O126" t="n">
-        <v>4.94</v>
+        <v>6.17</v>
       </c>
       <c r="P126" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Bamboo Sheets Queen Set-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
+          <t>Bamboo Sheets Olive-(VHSV)-Exact-(Ranking)-DO-BAMBOO-KING-OLIVE</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8889,20 +8889,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>VHSV</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6.39</v>
+        <v>6.47</v>
       </c>
       <c r="F127" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
@@ -8919,13 +8919,13 @@
         </is>
       </c>
       <c r="M127" t="n">
-        <v>5</v>
+        <v>7.33</v>
       </c>
       <c r="N127" t="n">
         <v>0</v>
       </c>
       <c r="O127" t="n">
-        <v>4.69</v>
+        <v>3.59</v>
       </c>
       <c r="P127" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Bamboo Sheets Twin-(MSV)-Exact-(Ranking)-DO-BAMBOO-TWIN-WHITE</t>
+          <t>Bamboo Sheets Organic-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8956,43 +8956,43 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>MSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E128" t="n">
         <v>6.47</v>
       </c>
       <c r="F128" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="G128" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>0.308</v>
+        <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>— → — → 20</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M128" t="n">
         <v>10</v>
       </c>
       <c r="N128" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
-        <v>3.86</v>
+        <v>4.94</v>
       </c>
       <c r="P128" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Bamboo Soft Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
+          <t>Bamboo Sheets Queen Set-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -9030,13 +9030,13 @@
         <v>6.39</v>
       </c>
       <c r="F129" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
@@ -9045,7 +9045,7 @@
         <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -9053,13 +9053,13 @@
         </is>
       </c>
       <c r="M129" t="n">
-        <v>8.869999999999999</v>
+        <v>5</v>
       </c>
       <c r="N129" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
-        <v>3.61</v>
+        <v>4.69</v>
       </c>
       <c r="P129" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Bed Sheets Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Bamboo Soft Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -9094,16 +9094,16 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6.47</v>
+        <v>6.39</v>
       </c>
       <c r="F130" t="n">
+        <v>15</v>
+      </c>
+      <c r="G130" t="n">
         <v>1</v>
       </c>
-      <c r="G130" t="n">
-        <v>0</v>
-      </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="I130" t="n">
         <v>0</v>
@@ -9112,7 +9112,7 @@
         <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -9120,13 +9120,13 @@
         </is>
       </c>
       <c r="M130" t="n">
-        <v>10</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="O130" t="n">
-        <v>4.46</v>
+        <v>3.61</v>
       </c>
       <c r="P130" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Bed Sheets Full Size Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE</t>
+          <t>Bed Sheets Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -9164,19 +9164,19 @@
         <v>6.47</v>
       </c>
       <c r="F131" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -9187,13 +9187,13 @@
         </is>
       </c>
       <c r="M131" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N131" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
-        <v>6.12</v>
+        <v>4.46</v>
       </c>
       <c r="P131" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Bed Sheets King Size Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Bed Sheets Full Size Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -9231,19 +9231,19 @@
         <v>6.47</v>
       </c>
       <c r="F132" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H132" t="n">
-        <v>0.278</v>
+        <v>0.2</v>
       </c>
       <c r="I132" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J132" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="M132" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="O132" t="n">
-        <v>3.51</v>
+        <v>6.12</v>
       </c>
       <c r="P132" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Black Cooling Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-BLACK</t>
+          <t>Bed Sheets King Size Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -9295,16 +9295,16 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5.18</v>
+        <v>6.47</v>
       </c>
       <c r="F133" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>0.3</v>
+        <v>0.278</v>
       </c>
       <c r="I133" t="n">
         <v>0</v>
@@ -9327,7 +9327,7 @@
         <v>0</v>
       </c>
       <c r="O133" t="n">
-        <v>3.61</v>
+        <v>3.51</v>
       </c>
       <c r="P133" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Buttery Soft Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Black Cooling Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-BLACK</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -9362,16 +9362,16 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6.47</v>
+        <v>5.18</v>
       </c>
       <c r="F134" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="I134" t="n">
         <v>0</v>
@@ -9388,13 +9388,13 @@
         </is>
       </c>
       <c r="M134" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N134" t="n">
         <v>0</v>
       </c>
       <c r="O134" t="n">
-        <v>4.69</v>
+        <v>3.61</v>
       </c>
       <c r="P134" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Cal King Bamboo Sheet Set-(LSV)-Exact-(Ranking)-FIX-BAMBOO-CALIFKING-WHITE</t>
+          <t>Buttery Soft Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -9425,29 +9425,29 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E135" t="n">
         <v>6.47</v>
       </c>
       <c r="F135" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G135" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>0.111</v>
+        <v>0.333</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -9455,13 +9455,13 @@
         </is>
       </c>
       <c r="M135" t="n">
-        <v>22.07</v>
+        <v>20</v>
       </c>
       <c r="N135" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
-        <v>6.89</v>
+        <v>4.69</v>
       </c>
       <c r="P135" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>California King Bamboo Sheet Sets-(LSV)-Exact-(Ranking)-FIX-BAMBOO-CALIFKING-WHITE</t>
+          <t>Cal King Bamboo Sheet Set-(LSV)-Exact-(Ranking)-FIX-BAMBOO-CALIFKING-WHITE</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -9499,40 +9499,40 @@
         <v>6.47</v>
       </c>
       <c r="F136" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G136" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H136" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K136" t="n">
         <v>1</v>
       </c>
-      <c r="I136" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K136" t="n">
-        <v>6</v>
-      </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>— → 22 → —</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M136" t="n">
-        <v>11.57</v>
+        <v>22.07</v>
       </c>
       <c r="N136" t="n">
-        <v>0.28</v>
+        <v>0.19</v>
       </c>
       <c r="O136" t="n">
-        <v>5.8</v>
+        <v>6.89</v>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>mod 61→78%; TOS $5.80→$6.41</t>
+          <t>holds</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>California King Cooling Sheets-[Cooling|California King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-CALIFKING-WHITE</t>
+          <t>California King Bamboo Sheet Sets-(LSV)-Exact-(Ranking)-FIX-BAMBOO-CALIFKING-WHITE</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -9563,43 +9563,43 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5.18</v>
+        <v>6.47</v>
       </c>
       <c r="F137" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G137" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="K137" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>— → 22 → —</t>
         </is>
       </c>
       <c r="M137" t="n">
-        <v>8</v>
+        <v>11.57</v>
       </c>
       <c r="N137" t="n">
-        <v>0.41</v>
+        <v>0.28</v>
       </c>
       <c r="O137" t="n">
-        <v>4.95</v>
+        <v>5.8</v>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>holds</t>
+          <t>mod 61→78%; TOS $5.80→$6.41</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>California King Sheet Sets Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-CALIFKING-WHITE</t>
+          <t>California King Cooling Sheets-[Cooling|California King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-CALIFKING-WHITE</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -9626,29 +9626,29 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6.47</v>
+        <v>5.18</v>
       </c>
       <c r="F138" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
       </c>
       <c r="I138" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J138" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="K138" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -9656,10 +9656,13 @@
         </is>
       </c>
       <c r="M138" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>0.41</v>
+      </c>
+      <c r="O138" t="n">
+        <v>4.95</v>
       </c>
       <c r="P138" t="inlineStr">
         <is>
@@ -9680,7 +9683,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>California King Sheet Sets Bamboo-[Bamboo|California King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-CALIFKING-WHITE</t>
+          <t>California King Sheet Sets Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-CALIFKING-WHITE</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9690,29 +9693,29 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E139" t="n">
         <v>6.47</v>
       </c>
       <c r="F139" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="G139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="I139" t="n">
         <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -9720,13 +9723,10 @@
         </is>
       </c>
       <c r="M139" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N139" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="O139" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="P139" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>California King Sheet Sets Cooling-[Cooling|California King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-CALIFKING-WHITE</t>
+          <t>California King Sheet Sets Bamboo-[Bamboo|California King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-CALIFKING-WHITE</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9761,25 +9761,25 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5.18</v>
+        <v>6.47</v>
       </c>
       <c r="F140" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H140" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
         <v>0.1</v>
       </c>
-      <c r="J140" t="n">
-        <v>0</v>
-      </c>
       <c r="K140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -9787,13 +9787,13 @@
         </is>
       </c>
       <c r="M140" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="O140" t="n">
-        <v>3.61</v>
+        <v>4.83</v>
       </c>
       <c r="P140" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>California King Sheets Bamboo-[Bamboo|California King]-(VLSV)-Exact-(Ranking)-DO-BAMBOO-CALIFKING-WHITE</t>
+          <t>California King Sheet Sets Cooling-[Cooling|California King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-CALIFKING-WHITE</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9824,20 +9824,20 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6.47</v>
+        <v>5.18</v>
       </c>
       <c r="F141" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I141" t="n">
         <v>0.1</v>
@@ -9846,7 +9846,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -9854,13 +9854,13 @@
         </is>
       </c>
       <c r="M141" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N141" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
-        <v>4.75</v>
+        <v>3.61</v>
       </c>
       <c r="P141" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Cool Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>California King Sheets Bamboo-[Bamboo|California King]-(VLSV)-Exact-(Ranking)-DO-BAMBOO-CALIFKING-WHITE</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9895,25 +9895,25 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5.18</v>
+        <v>6.47</v>
       </c>
       <c r="F142" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H142" t="n">
-        <v>0.111</v>
+        <v>0.5</v>
       </c>
       <c r="I142" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
@@ -9924,10 +9924,10 @@
         <v>5</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="O142" t="n">
-        <v>3.59</v>
+        <v>4.75</v>
       </c>
       <c r="P142" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Cool Sheets For Hot Sleepers-[Cooling]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
+          <t>Cool Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9958,20 +9958,20 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>3.61</v>
+        <v>5.18</v>
       </c>
       <c r="F143" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G143" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>0.5</v>
+        <v>0.111</v>
       </c>
       <c r="I143" t="n">
         <v>0</v>
@@ -9984,17 +9984,17 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>— → 68 → 3</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M143" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N143" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
-        <v>2.56</v>
+        <v>3.59</v>
       </c>
       <c r="P143" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Cooling Bamboo Sheets-[Bamboo|Cooling]-(MSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Cool Sheets For Hot Sleepers-[Cooling]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -10025,43 +10025,43 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>MSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5.68</v>
+        <v>3.61</v>
       </c>
       <c r="F144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G144" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H144" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I144" t="n">
         <v>0</v>
       </c>
       <c r="J144" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>— → 68 → 3</t>
         </is>
       </c>
       <c r="M144" t="n">
         <v>10</v>
       </c>
       <c r="N144" t="n">
-        <v>0.19</v>
+        <v>0.05</v>
       </c>
       <c r="O144" t="n">
-        <v>4.6</v>
+        <v>2.56</v>
       </c>
       <c r="P144" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Cooling Bed Sheets Queen-(MSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
+          <t>Cooling Bamboo Sheets-[Bamboo|Cooling]-(MSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -10096,13 +10096,13 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5.18</v>
+        <v>5.68</v>
       </c>
       <c r="F145" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -10111,10 +10111,10 @@
         <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="K145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -10122,13 +10122,13 @@
         </is>
       </c>
       <c r="M145" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="O145" t="n">
-        <v>3.61</v>
+        <v>4.6</v>
       </c>
       <c r="P145" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Cooling Bed Sheets-(HSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Cooling Bed Sheets Queen-(MSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -10159,40 +10159,43 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>HSV</t>
+          <t>MSV</t>
         </is>
       </c>
       <c r="E146" t="n">
         <v>5.18</v>
       </c>
       <c r="F146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
       </c>
       <c r="I146" t="n">
         <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>— → — → 9</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M146" t="n">
         <v>18</v>
       </c>
       <c r="N146" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
-        <v>3.29</v>
+        <v>3.61</v>
       </c>
       <c r="P146" t="inlineStr">
         <is>
@@ -10213,7 +10216,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Cooling Bedsheets Queen Size-[Cooling|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
+          <t>Cooling Bed Sheets-(HSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -10223,20 +10226,17 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6.19</v>
+        <v>5.18</v>
       </c>
       <c r="F147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>2</v>
-      </c>
-      <c r="H147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I147" t="n">
         <v>0</v>
@@ -10249,17 +10249,17 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>— → — → 9</t>
         </is>
       </c>
       <c r="M147" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="N147" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="O147" t="n">
-        <v>4.94</v>
+        <v>3.29</v>
       </c>
       <c r="P147" t="inlineStr">
         <is>
@@ -10280,7 +10280,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Cooling Fitted Sheet Queen-(MSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
+          <t>Cooling Bedsheets Queen Size-[Cooling|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -10290,17 +10290,17 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>MSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>5.18</v>
+        <v>6.19</v>
       </c>
       <c r="F148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -10312,18 +10312,18 @@
         <v>0.1</v>
       </c>
       <c r="K148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>— → — → 7</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M148" t="n">
         <v>10</v>
       </c>
       <c r="N148" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="O148" t="n">
         <v>4.94</v>
@@ -10347,7 +10347,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Cooling Full Size Sheets-[Cooling|Full]-(LSV)-Exact-(Ranking)-DO-BAMBOO-FULL-LIGHTBLUE</t>
+          <t>Cooling Fitted Sheet Queen-(MSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -10357,43 +10357,43 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>MSV</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6.19</v>
+        <v>5.18</v>
       </c>
       <c r="F149" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
       </c>
       <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
         <v>0.1</v>
       </c>
-      <c r="J149" t="n">
-        <v>0</v>
-      </c>
       <c r="K149" t="n">
         <v>0</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>— → — → 7</t>
         </is>
       </c>
       <c r="M149" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O149" t="n">
-        <v>3.61</v>
+        <v>4.94</v>
       </c>
       <c r="P149" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Cooling Sheet-[Cooling]-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-2</t>
+          <t>Cooling Full Size Sheets-[Cooling|Full]-(LSV)-Exact-(Ranking)-DO-BAMBOO-FULL-LIGHTBLUE</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -10428,39 +10428,39 @@
         </is>
       </c>
       <c r="E150" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="F150" t="n">
+        <v>8</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>— → — → —</t>
+        </is>
+      </c>
+      <c r="M150" t="n">
+        <v>5</v>
+      </c>
+      <c r="N150" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" t="n">
         <v>3.61</v>
-      </c>
-      <c r="F150" t="n">
-        <v>6</v>
-      </c>
-      <c r="G150" t="n">
-        <v>4</v>
-      </c>
-      <c r="H150" t="n">
-        <v>0</v>
-      </c>
-      <c r="I150" t="n">
-        <v>0</v>
-      </c>
-      <c r="J150" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K150" t="n">
-        <v>1</v>
-      </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>— → — → —</t>
-        </is>
-      </c>
-      <c r="M150" t="n">
-        <v>10</v>
-      </c>
-      <c r="N150" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="O150" t="n">
-        <v>6</v>
       </c>
       <c r="P150" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Cooling Sheets For Hot Sleepers-[Cooling]-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Cooling Sheet-[Cooling]-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-2</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -10498,36 +10498,36 @@
         <v>3.61</v>
       </c>
       <c r="F151" t="n">
+        <v>6</v>
+      </c>
+      <c r="G151" t="n">
+        <v>4</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K151" t="n">
         <v>1</v>
       </c>
-      <c r="G151" t="n">
-        <v>0</v>
-      </c>
-      <c r="H151" t="n">
-        <v>0</v>
-      </c>
-      <c r="I151" t="n">
-        <v>0</v>
-      </c>
-      <c r="J151" t="n">
-        <v>0</v>
-      </c>
-      <c r="K151" t="n">
-        <v>0</v>
-      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>— → — → —</t>
         </is>
       </c>
       <c r="M151" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="O151" t="n">
-        <v>3.22</v>
+        <v>6</v>
       </c>
       <c r="P151" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Cooling Sheets-[Cooling]-(VHSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Cooling Sheets For Hot Sleepers-[Cooling]-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -10558,7 +10558,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VHSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E152" t="n">
@@ -10571,7 +10571,7 @@
         <v>0</v>
       </c>
       <c r="H152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I152" t="n">
         <v>0</v>
@@ -10584,17 +10584,17 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>— → — → 11</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M152" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="N152" t="n">
         <v>0</v>
       </c>
       <c r="O152" t="n">
-        <v>1.33</v>
+        <v>3.22</v>
       </c>
       <c r="P152" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Decolure Bamboo Sheets King Size-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Cooling Sheets-[Cooling]-(VHSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -10625,47 +10625,47 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>VHSV</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6.47</v>
+        <v>3.61</v>
       </c>
       <c r="F153" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="G153" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>0.459</v>
+        <v>1</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>54 → 64 → 11</t>
         </is>
       </c>
       <c r="M153" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="N153" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
-        <v>2.41</v>
+        <v>1.33</v>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>mod 18→16%; TOS $2.41→$2.37</t>
+          <t>holds</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Decolure-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Decolure Bamboo Sheets King Size-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -10699,22 +10699,22 @@
         <v>6.47</v>
       </c>
       <c r="F154" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="G154" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H154" t="n">
-        <v>0.108</v>
+        <v>0.459</v>
       </c>
       <c r="I154" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J154" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="K154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -10725,14 +10725,14 @@
         <v>5</v>
       </c>
       <c r="N154" t="n">
-        <v>0.02</v>
+        <v>0.21</v>
       </c>
       <c r="O154" t="n">
-        <v>3.72</v>
+        <v>2.41</v>
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>holds</t>
+          <t>mod 18→16%; TOS $2.41→$2.37</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Deep Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Decolure-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -10766,22 +10766,22 @@
         <v>6.47</v>
       </c>
       <c r="F155" t="n">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H155" t="n">
-        <v>0.333</v>
+        <v>0.108</v>
       </c>
       <c r="I155" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="J155" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -10792,10 +10792,10 @@
         <v>5</v>
       </c>
       <c r="N155" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="O155" t="n">
-        <v>4.37</v>
+        <v>3.72</v>
       </c>
       <c r="P155" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Full Bamboo Bed Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE</t>
+          <t>Deep Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -10833,13 +10833,13 @@
         <v>6.47</v>
       </c>
       <c r="F156" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="I156" t="n">
         <v>0</v>
@@ -10862,7 +10862,7 @@
         <v>0</v>
       </c>
       <c r="O156" t="n">
-        <v>4.69</v>
+        <v>4.37</v>
       </c>
       <c r="P156" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Full Bamboo Sheets Sets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE</t>
+          <t>Full Bamboo Bed Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10900,10 +10900,10 @@
         <v>6.47</v>
       </c>
       <c r="F157" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G157" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -10912,10 +10912,10 @@
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="K157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -10926,10 +10926,10 @@
         <v>5</v>
       </c>
       <c r="N157" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
-        <v>4.75</v>
+        <v>4.69</v>
       </c>
       <c r="P157" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Full Bed Sheets Cooling-[Cooling|Full]-(LSV)-Exact-(Ranking)-DO-BAMBOO-FULL-LIGHTBLUE</t>
+          <t>Full Bamboo Sheets Sets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10960,17 +10960,17 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6.19</v>
+        <v>6.47</v>
       </c>
       <c r="F158" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -10979,10 +10979,10 @@
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="K158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -10990,10 +10990,13 @@
         </is>
       </c>
       <c r="M158" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>0.27</v>
+      </c>
+      <c r="O158" t="n">
+        <v>4.75</v>
       </c>
       <c r="P158" t="inlineStr">
         <is>
@@ -11014,7 +11017,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Full Sheet Set Bamboo-[Bamboo|Full]-(VLSV)-Exact-(Ranking)-DO-BAMBOO-FULL-OLIVE</t>
+          <t>Full Bed Sheets Cooling-[Cooling|Full]-(LSV)-Exact-(Ranking)-DO-BAMBOO-FULL-LIGHTBLUE</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -11024,17 +11027,17 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>7.22</v>
+        <v>6.19</v>
       </c>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G159" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -11043,7 +11046,7 @@
         <v>0</v>
       </c>
       <c r="J159" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K159" t="n">
         <v>0</v>
@@ -11057,10 +11060,7 @@
         <v>10</v>
       </c>
       <c r="N159" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="O159" t="n">
-        <v>5.46</v>
+        <v>0</v>
       </c>
       <c r="P159" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Full Size Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE</t>
+          <t>Full Sheet Set Bamboo-[Bamboo|Full]-(VLSV)-Exact-(Ranking)-DO-BAMBOO-FULL-OLIVE</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -11095,43 +11095,43 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6.47</v>
+        <v>7.22</v>
       </c>
       <c r="F160" t="n">
-        <v>81</v>
+        <v>3</v>
       </c>
       <c r="G160" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H160" t="n">
-        <v>0.593</v>
+        <v>0</v>
       </c>
       <c r="I160" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J160" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="K160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>— → 49 → 15</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M160" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N160" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="O160" t="n">
-        <v>6.4</v>
+        <v>5.46</v>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>mod 493→558%; base ↓10%; TOS $6.40→$6.38</t>
+          <t>holds</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Full Size Bed Sheets Bamboo-[Bamboo|Full]-(LSV)-Exact-(Ranking)-DO-BAMBOO-FULL-OLIVE</t>
+          <t>Full Size Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -11158,47 +11158,47 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>7.22</v>
+        <v>6.47</v>
       </c>
       <c r="F161" t="n">
+        <v>81</v>
+      </c>
+      <c r="G161" t="n">
+        <v>9</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K161" t="n">
+        <v>1</v>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>— → 49 → 15</t>
+        </is>
+      </c>
+      <c r="M161" t="n">
         <v>12</v>
       </c>
-      <c r="G161" t="n">
-        <v>0</v>
-      </c>
-      <c r="H161" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="I161" t="n">
-        <v>0</v>
-      </c>
-      <c r="J161" t="n">
-        <v>0</v>
-      </c>
-      <c r="K161" t="n">
-        <v>0</v>
-      </c>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>— → — → —</t>
-        </is>
-      </c>
-      <c r="M161" t="n">
-        <v>5</v>
-      </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O161" t="n">
-        <v>2.61</v>
+        <v>6.4</v>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>holds</t>
+          <t>mod 493→558%; base ↓10%; TOS $6.40→$6.38</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
@@ -11215,7 +11215,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Full Size Sheet Sets Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE</t>
+          <t>Full Size Bed Sheets Bamboo-[Bamboo|Full]-(LSV)-Exact-(Ranking)-DO-BAMBOO-FULL-OLIVE</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -11225,23 +11225,23 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6.47</v>
+        <v>7.22</v>
       </c>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="I162" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -11255,13 +11255,13 @@
         </is>
       </c>
       <c r="M162" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N162" t="n">
         <v>0</v>
       </c>
       <c r="O162" t="n">
-        <v>4.69</v>
+        <v>2.61</v>
       </c>
       <c r="P162" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Hypoallergenic Sheets-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Full Size Sheet Sets Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -11292,17 +11292,17 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E163" t="n">
         <v>6.47</v>
       </c>
       <c r="F163" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G163" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -11311,7 +11311,7 @@
         <v>0.1</v>
       </c>
       <c r="J163" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="K163" t="n">
         <v>0</v>
@@ -11322,13 +11322,13 @@
         </is>
       </c>
       <c r="M163" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N163" t="n">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
-        <v>4.98</v>
+        <v>4.69</v>
       </c>
       <c r="P163" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>King Sheets Bamboo Deep Pocket-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Hypoallergenic Sheets-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -11359,29 +11359,29 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E164" t="n">
         <v>6.47</v>
       </c>
       <c r="F164" t="n">
+        <v>6</v>
+      </c>
+      <c r="G164" t="n">
         <v>4</v>
       </c>
-      <c r="G164" t="n">
-        <v>2</v>
-      </c>
       <c r="H164" t="n">
         <v>0</v>
       </c>
       <c r="I164" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J164" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="K164" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -11389,13 +11389,13 @@
         </is>
       </c>
       <c r="M164" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N164" t="n">
-        <v>0.13</v>
+        <v>0.43</v>
       </c>
       <c r="O164" t="n">
-        <v>4.69</v>
+        <v>4.98</v>
       </c>
       <c r="P164" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>King Sheets Bamboo Viscose-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>King Sheets Bamboo Deep Pocket-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -11442,13 +11442,13 @@
         <v>0</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J165" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="K165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -11456,13 +11456,13 @@
         </is>
       </c>
       <c r="M165" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N165" t="n">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="O165" t="n">
-        <v>6.17</v>
+        <v>4.69</v>
       </c>
       <c r="P165" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>King Size Bamboo Bed Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>King Sheets Bamboo Viscose-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -11500,22 +11500,22 @@
         <v>6.47</v>
       </c>
       <c r="F166" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G166" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H166" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J166" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -11526,10 +11526,10 @@
         <v>5</v>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="O166" t="n">
-        <v>4.42</v>
+        <v>6.17</v>
       </c>
       <c r="P166" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>King Size Bamboo Sheets Set Deep Pocket-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>King Size Bamboo Bed Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -11567,13 +11567,13 @@
         <v>6.47</v>
       </c>
       <c r="F167" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>0.133</v>
+        <v>0.2</v>
       </c>
       <c r="I167" t="n">
         <v>0</v>
@@ -11590,13 +11590,13 @@
         </is>
       </c>
       <c r="M167" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="N167" t="n">
         <v>0</v>
       </c>
       <c r="O167" t="n">
-        <v>1.9</v>
+        <v>4.42</v>
       </c>
       <c r="P167" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>King Size Deep Pocket Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>King Size Bamboo Sheets Set Deep Pocket-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -11634,13 +11634,13 @@
         <v>6.47</v>
       </c>
       <c r="F168" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H168" t="n">
-        <v>0.077</v>
+        <v>0.133</v>
       </c>
       <c r="I168" t="n">
         <v>0</v>
@@ -11663,7 +11663,7 @@
         <v>0</v>
       </c>
       <c r="O168" t="n">
-        <v>3.59</v>
+        <v>1.9</v>
       </c>
       <c r="P168" t="inlineStr">
         <is>
@@ -11684,7 +11684,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Luxury Bamboo Bed Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>King Size Deep Pocket Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -11701,13 +11701,13 @@
         <v>6.47</v>
       </c>
       <c r="F169" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H169" t="n">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="I169" t="n">
         <v>0</v>
@@ -11724,13 +11724,13 @@
         </is>
       </c>
       <c r="M169" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N169" t="n">
         <v>0</v>
       </c>
       <c r="O169" t="n">
-        <v>5.81</v>
+        <v>3.59</v>
       </c>
       <c r="P169" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Luxury King Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Luxury Bamboo Bed Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -11768,22 +11768,22 @@
         <v>6.47</v>
       </c>
       <c r="F170" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="G170" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H170" t="n">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="I170" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J170" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -11794,10 +11794,10 @@
         <v>10</v>
       </c>
       <c r="N170" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="O170" t="n">
-        <v>3.61</v>
+        <v>5.81</v>
       </c>
       <c r="P170" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Natural Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Luxury King Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -11835,22 +11835,22 @@
         <v>6.47</v>
       </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H171" t="n">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="I171" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J171" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -11858,13 +11858,13 @@
         </is>
       </c>
       <c r="M171" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N171" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="O171" t="n">
-        <v>4.69</v>
+        <v>3.61</v>
       </c>
       <c r="P171" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Queen Cooling Sheet Set-[Cooling|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
+          <t>Natural Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -11895,14 +11895,14 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6.19</v>
+        <v>6.47</v>
       </c>
       <c r="F172" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -11925,10 +11925,13 @@
         </is>
       </c>
       <c r="M172" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N172" t="n">
         <v>0</v>
+      </c>
+      <c r="O172" t="n">
+        <v>4.69</v>
       </c>
       <c r="P172" t="inlineStr">
         <is>
@@ -11949,7 +11952,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Queen Cooling Sheets Deep Pockets-[Cooling|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
+          <t>Queen Cooling Sheet Set-[Cooling|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11989,7 +11992,7 @@
         </is>
       </c>
       <c r="M173" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N173" t="n">
         <v>0</v>
@@ -12013,7 +12016,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Queen Cooling Sheets-[Cooling|Queen]-(MSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
+          <t>Queen Cooling Sheets Deep Pockets-[Cooling|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -12023,20 +12026,20 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>MSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E174" t="n">
         <v>6.19</v>
       </c>
       <c r="F174" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G174" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H174" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="I174" t="n">
         <v>0</v>
@@ -12045,18 +12048,18 @@
         <v>0</v>
       </c>
       <c r="K174" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>— → — → 8</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M174" t="n">
         <v>5</v>
       </c>
       <c r="N174" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P174" t="inlineStr">
         <is>
@@ -12077,7 +12080,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Queen Deep Pocket Bamboo Sheet Sets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
+          <t>Queen Cooling Sheets-[Cooling|Queen]-(MSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -12087,43 +12090,40 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>MSV</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6.39</v>
+        <v>6.19</v>
       </c>
       <c r="F175" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G175" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H175" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I175" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" t="n">
+        <v>4</v>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>— → — → 8</t>
+        </is>
+      </c>
+      <c r="M175" t="n">
+        <v>5</v>
+      </c>
+      <c r="N175" t="n">
         <v>0.1</v>
-      </c>
-      <c r="J175" t="n">
-        <v>0</v>
-      </c>
-      <c r="K175" t="n">
-        <v>0</v>
-      </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>— → — → —</t>
-        </is>
-      </c>
-      <c r="M175" t="n">
-        <v>6</v>
-      </c>
-      <c r="N175" t="n">
-        <v>0</v>
-      </c>
-      <c r="O175" t="n">
-        <v>4.69</v>
       </c>
       <c r="P175" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Queen Sheet Set Cooling-[Cooling|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
+          <t>Queen Deep Pocket Bamboo Sheet Sets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -12154,26 +12154,26 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6.19</v>
+        <v>6.39</v>
       </c>
       <c r="F176" t="n">
         <v>3</v>
       </c>
       <c r="G176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H176" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="I176" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J176" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K176" t="n">
         <v>0</v>
@@ -12184,13 +12184,13 @@
         </is>
       </c>
       <c r="M176" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N176" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="O176" t="n">
-        <v>4.94</v>
+        <v>4.69</v>
       </c>
       <c r="P176" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Queen Sheets Deep Pocket Cooling-[Cooling|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
+          <t>Queen Sheet Set Cooling-[Cooling|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -12228,19 +12228,19 @@
         <v>6.19</v>
       </c>
       <c r="F177" t="n">
+        <v>3</v>
+      </c>
+      <c r="G177" t="n">
         <v>1</v>
       </c>
-      <c r="G177" t="n">
-        <v>0</v>
-      </c>
       <c r="H177" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="I177" t="n">
         <v>0</v>
       </c>
       <c r="J177" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K177" t="n">
         <v>0</v>
@@ -12254,10 +12254,10 @@
         <v>10</v>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O177" t="n">
-        <v>4.74</v>
+        <v>4.94</v>
       </c>
       <c r="P177" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Red Queen Bedding-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-BURGUNDY-NEW</t>
+          <t>Queen Sheets Deep Pocket Cooling-[Cooling|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -12288,11 +12288,11 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6.39</v>
+        <v>6.19</v>
       </c>
       <c r="F178" t="n">
         <v>1</v>
@@ -12318,13 +12318,13 @@
         </is>
       </c>
       <c r="M178" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N178" t="n">
         <v>0</v>
       </c>
       <c r="O178" t="n">
-        <v>3.95</v>
+        <v>4.74</v>
       </c>
       <c r="P178" t="inlineStr">
         <is>
@@ -12345,7 +12345,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Sheets Bamboo King Size Bed Set-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>Red Queen Bedding-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-BURGUNDY-NEW</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -12359,16 +12359,16 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6.47</v>
+        <v>6.39</v>
       </c>
       <c r="F179" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
       </c>
       <c r="H179" t="n">
-        <v>0.231</v>
+        <v>0</v>
       </c>
       <c r="I179" t="n">
         <v>0</v>
@@ -12385,13 +12385,13 @@
         </is>
       </c>
       <c r="M179" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N179" t="n">
         <v>0</v>
       </c>
       <c r="O179" t="n">
-        <v>1.9</v>
+        <v>3.95</v>
       </c>
       <c r="P179" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Sheets Full Size Bed Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE</t>
+          <t>Sheets Bamboo King Size Bed Set-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -12429,13 +12429,13 @@
         <v>6.47</v>
       </c>
       <c r="F180" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G180" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H180" t="n">
-        <v>0.947</v>
+        <v>0.231</v>
       </c>
       <c r="I180" t="n">
         <v>0</v>
@@ -12444,7 +12444,7 @@
         <v>0</v>
       </c>
       <c r="K180" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
@@ -12452,17 +12452,17 @@
         </is>
       </c>
       <c r="M180" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N180" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="O180" t="n">
-        <v>6.42</v>
+        <v>1.9</v>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>mod 147→174%; TOS $6.42→$7.12</t>
+          <t>holds</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Sheets Queen Size Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
+          <t>Sheets Full Size Bed Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -12493,16 +12493,16 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6.39</v>
+        <v>6.47</v>
       </c>
       <c r="F181" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G181" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H181" t="n">
-        <v>0</v>
+        <v>0.947</v>
       </c>
       <c r="I181" t="n">
         <v>0</v>
@@ -12511,7 +12511,7 @@
         <v>0</v>
       </c>
       <c r="K181" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L181" t="inlineStr">
         <is>
@@ -12519,17 +12519,17 @@
         </is>
       </c>
       <c r="M181" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="O181" t="n">
-        <v>4.94</v>
+        <v>6.42</v>
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>holds</t>
+          <t>mod 147→174%; TOS $6.42→$7.12</t>
         </is>
       </c>
       <c r="Q181" t="inlineStr">
@@ -12546,7 +12546,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Twin Bamboo Sheets Set-(LSV)-Exact-(Ranking)-DO-BAMBOO-TWIN-WHITE</t>
+          <t>Sheets Queen Size Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -12556,29 +12556,29 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6.47</v>
+        <v>6.39</v>
       </c>
       <c r="F182" t="n">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="G182" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H182" t="n">
-        <v>0.652</v>
+        <v>0</v>
       </c>
       <c r="I182" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J182" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="K182" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
@@ -12586,17 +12586,17 @@
         </is>
       </c>
       <c r="M182" t="n">
-        <v>6.68</v>
+        <v>10</v>
       </c>
       <c r="N182" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="O182" t="n">
-        <v>5.68</v>
+        <v>4.94</v>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>mod 163→217%; base ↓17%</t>
+          <t>holds</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Twin Bamboo Sheets-[Bamboo|Twin]-(LSV)-Exact-(Ranking)-DO-BAMBOO-TWIN-BURGUNDY-NEW</t>
+          <t>Twin Bamboo Sheets Set-(LSV)-Exact-(Ranking)-DO-BAMBOO-TWIN-WHITE</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -12627,43 +12627,43 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6.06</v>
+        <v>6.47</v>
       </c>
       <c r="F183" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="G183" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H183" t="n">
-        <v>0.636</v>
+        <v>0.652</v>
       </c>
       <c r="I183" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="J183" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="K183" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>— → 53 → 20</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M183" t="n">
-        <v>10</v>
+        <v>6.68</v>
       </c>
       <c r="N183" t="n">
-        <v>0.22</v>
+        <v>1.01</v>
       </c>
       <c r="O183" t="n">
-        <v>4.6</v>
+        <v>5.68</v>
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>mod 154→182%; TOS $4.60→$5.10</t>
+          <t>mod 163→217%; base ↓17%</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Twin Bed Sheets Cooling-[Cooling|Twin]-(LSV)-Exact-(Ranking)-DO-BAMBOO-TWIN-LIGHTBLUE</t>
+          <t>Twin Bamboo Sheets-[Bamboo|Twin]-(LSV)-Exact-(Ranking)-DO-BAMBOO-TWIN-BURGUNDY-NEW</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -12694,40 +12694,43 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6.19</v>
+        <v>6.06</v>
       </c>
       <c r="F184" t="n">
+        <v>11</v>
+      </c>
+      <c r="G184" t="n">
+        <v>8</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="I184" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J184" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K184" t="n">
         <v>1</v>
       </c>
-      <c r="G184" t="n">
-        <v>0</v>
-      </c>
-      <c r="H184" t="n">
-        <v>0</v>
-      </c>
-      <c r="I184" t="n">
-        <v>0</v>
-      </c>
-      <c r="J184" t="n">
-        <v>0</v>
-      </c>
-      <c r="K184" t="n">
-        <v>0</v>
-      </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>— → 53 → 20</t>
         </is>
       </c>
       <c r="M184" t="n">
         <v>10</v>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>0.22</v>
+      </c>
+      <c r="O184" t="n">
+        <v>4.6</v>
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>holds</t>
+          <t>mod 154→182%; TOS $4.60→$5.10</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
@@ -12744,7 +12747,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Twin Cooling Sheets-[Cooling|Twin]-(LSV)-Exact-(Ranking)-DO-BAMBOO-TWIN-LIGHTBLUE</t>
+          <t>Twin Bed Sheets Cooling-[Cooling|Twin]-(LSV)-Exact-(Ranking)-DO-BAMBOO-TWIN-LIGHTBLUE</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -12761,40 +12764,37 @@
         <v>6.19</v>
       </c>
       <c r="F185" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="G185" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H185" t="n">
-        <v>0.464</v>
+        <v>0</v>
       </c>
       <c r="I185" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J185" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K185" t="n">
         <v>0</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>— → 34 → 52</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M185" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N185" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="O185" t="n">
-        <v>7.51</v>
+        <v>0</v>
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>mod 496→571%; base ↓11%</t>
+          <t>holds</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
@@ -12811,7 +12811,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Twin Sheets Cooling-[Cooling|Twin]-(LSV)-Exact-(Ranking)-DO-BAMBOO-TWIN-LIGHTBLUE</t>
+          <t>Twin Cooling Sheets-[Cooling|Twin]-(LSV)-Exact-(Ranking)-DO-BAMBOO-TWIN-LIGHTBLUE</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -12828,37 +12828,40 @@
         <v>6.19</v>
       </c>
       <c r="F186" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="G186" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H186" t="n">
-        <v>0</v>
+        <v>0.464</v>
       </c>
       <c r="I186" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J186" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K186" t="n">
         <v>0</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>— → 34 → 52</t>
         </is>
       </c>
       <c r="M186" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>0.16</v>
+      </c>
+      <c r="O186" t="n">
+        <v>7.51</v>
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>holds</t>
+          <t>mod 496→571%; base ↓11%</t>
         </is>
       </c>
       <c r="Q186" t="inlineStr">
@@ -12875,7 +12878,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>king size sheets set bamboo cooling-[Bamboo|Cooling]-(LSV)-Exact-(Ranking)-FIX-BAMBOO-KING-WHITE</t>
+          <t>Twin Sheets Cooling-[Cooling|Twin]-(LSV)-Exact-(Ranking)-DO-BAMBOO-TWIN-LIGHTBLUE</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -12889,22 +12892,22 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>5.68</v>
+        <v>6.19</v>
       </c>
       <c r="F187" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G187" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H187" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="I187" t="n">
         <v>0</v>
       </c>
       <c r="J187" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K187" t="n">
         <v>0</v>
@@ -12915,13 +12918,10 @@
         </is>
       </c>
       <c r="M187" t="n">
-        <v>11.42</v>
+        <v>10</v>
       </c>
       <c r="N187" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="O187" t="n">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="P187" t="inlineStr">
         <is>
@@ -12937,12 +12937,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>B · Out of focus, went dark — restore</t>
+          <t>B · Out of focus, thin — hold</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Bamboo Cooling Sheets King Size-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
+          <t>king size sheets set bamboo cooling-[Bamboo|Cooling]-(LSV)-Exact-(Ranking)-FIX-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -12956,48 +12956,48 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>5.18</v>
+        <v>5.68</v>
       </c>
       <c r="F188" t="n">
-        <v>247</v>
+        <v>3</v>
       </c>
       <c r="G188" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H188" t="n">
-        <v>0.551</v>
+        <v>0.333</v>
       </c>
       <c r="I188" t="n">
+        <v>0</v>
+      </c>
+      <c r="J188" t="n">
         <v>0.2</v>
       </c>
-      <c r="J188" t="n">
-        <v>0</v>
-      </c>
       <c r="K188" t="n">
         <v>0</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>— → 13 → —</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M188" t="n">
-        <v>5</v>
+        <v>11.42</v>
       </c>
       <c r="N188" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="O188" t="n">
-        <v>2.55</v>
+        <v>5.32</v>
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>budget $5→$6.5</t>
+          <t>holds</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>Restore pre-cut prices and read next day; if already restored or never changed, check eligibility</t>
+          <t>Hold flat — no cut, no raise</t>
         </is>
       </c>
     </row>
@@ -13009,7 +13009,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Cal King Bamboo Sheets-[Bamboo|California King]-(VLSV)-Exact-(Ranking)-DO-BAMBOO-CALIFKING-WHITE</t>
+          <t>Bamboo Cooling Sheets King Size-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -13019,23 +13019,23 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6.47</v>
+        <v>5.18</v>
       </c>
       <c r="F189" t="n">
-        <v>58</v>
+        <v>247</v>
       </c>
       <c r="G189" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H189" t="n">
-        <v>0.569</v>
+        <v>0.551</v>
       </c>
       <c r="I189" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -13045,21 +13045,21 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>— → 13 → —</t>
         </is>
       </c>
       <c r="M189" t="n">
-        <v>8.23</v>
+        <v>5</v>
       </c>
       <c r="N189" t="n">
         <v>0</v>
       </c>
       <c r="O189" t="n">
-        <v>3.84</v>
+        <v>2.55</v>
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>holds</t>
+          <t>budget $5→$6.5</t>
         </is>
       </c>
       <c r="Q189" t="inlineStr">
@@ -13076,7 +13076,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Cooling Bamboo Sheets Queen Size-[Bamboo|Cooling]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
+          <t>Cal King Bamboo Sheets-[Bamboo|California King]-(VLSV)-Exact-(Ranking)-DO-BAMBOO-CALIFKING-WHITE</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -13086,20 +13086,20 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>5.68</v>
+        <v>6.47</v>
       </c>
       <c r="F190" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="G190" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H190" t="n">
-        <v>0.063</v>
+        <v>0.569</v>
       </c>
       <c r="I190" t="n">
         <v>0.1</v>
@@ -13116,13 +13116,13 @@
         </is>
       </c>
       <c r="M190" t="n">
-        <v>9.94</v>
+        <v>8.23</v>
       </c>
       <c r="N190" t="n">
         <v>0</v>
       </c>
       <c r="O190" t="n">
-        <v>1.67</v>
+        <v>3.84</v>
       </c>
       <c r="P190" t="inlineStr">
         <is>
@@ -13138,12 +13138,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>B · Out of focus, working — hold flat</t>
+          <t>B · Out of focus, went dark — restore</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Bamboo Cooling Sheets-(MSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
+          <t>Cooling Bamboo Sheets Queen Size-[Bamboo|Cooling]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -13153,52 +13153,52 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>MSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5.18</v>
+        <v>5.68</v>
       </c>
       <c r="F191" t="n">
-        <v>410</v>
+        <v>63</v>
       </c>
       <c r="G191" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="H191" t="n">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="I191" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="J191" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="K191" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>— → 28 → 5</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M191" t="n">
-        <v>31</v>
+        <v>9.94</v>
       </c>
       <c r="N191" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="O191" t="n">
-        <v>7.61</v>
+        <v>1.67</v>
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>mod 718→818%; base ↓11%; TOS $7.61→$7.62</t>
+          <t>holds</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>Hold flat — no cut, no raise</t>
+          <t>Restore pre-cut prices and read next day; if already restored or never changed, check eligibility</t>
         </is>
       </c>
     </row>
@@ -13210,7 +13210,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Bamboo Sheets Full Size-[Bamboo|Full]-(MSV)-Exact-(Ranking)-DO-BAMBOO-FULL-OLIVE</t>
+          <t>Bamboo Cooling Sheets-(MSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -13224,43 +13224,43 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>7.22</v>
+        <v>5.18</v>
       </c>
       <c r="F192" t="n">
-        <v>188</v>
+        <v>410</v>
       </c>
       <c r="G192" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H192" t="n">
-        <v>0.186</v>
+        <v>0</v>
       </c>
       <c r="I192" t="n">
         <v>0.7</v>
       </c>
       <c r="J192" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="K192" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>— → 44 → 10</t>
+          <t>45 → 28 → 5</t>
         </is>
       </c>
       <c r="M192" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N192" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.29</v>
       </c>
       <c r="O192" t="n">
-        <v>4.96</v>
+        <v>7.61</v>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>mod 351→451%; base ↓10%; TOS $4.96→$5.45</t>
+          <t>mod 718→818%; base ↓11%; TOS $7.61→$7.62</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
@@ -16541,10 +16541,10 @@
         <v>33</v>
       </c>
       <c r="S2" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="T2" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -16617,10 +16617,10 @@
         <v>25</v>
       </c>
       <c r="S3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="T3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -16693,10 +16693,10 @@
         <v>35</v>
       </c>
       <c r="S4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="T4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -16763,10 +16763,10 @@
         <v>28</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T5" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -16833,10 +16833,10 @@
         <v>55</v>
       </c>
       <c r="S6" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="T6" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>29</v>
       </c>
       <c r="S7" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="T7" t="n">
         <v>71</v>
@@ -16982,7 +16982,7 @@
         <v>30</v>
       </c>
       <c r="T8" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -17052,10 +17052,10 @@
         <v>55</v>
       </c>
       <c r="S9" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="T9" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -17122,10 +17122,10 @@
         <v>24</v>
       </c>
       <c r="S10" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="T10" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -17250,10 +17250,10 @@
         <v>30</v>
       </c>
       <c r="S12" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="T12" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -17320,10 +17320,10 @@
         <v>120</v>
       </c>
       <c r="S13" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="T13" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -17390,10 +17390,10 @@
         <v>24</v>
       </c>
       <c r="S14" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T14" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -17454,10 +17454,10 @@
         <v>17</v>
       </c>
       <c r="S15" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -17524,10 +17524,10 @@
         <v>31</v>
       </c>
       <c r="S16" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="T16" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -17588,10 +17588,10 @@
         <v>36</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -17652,10 +17652,10 @@
         <v>42</v>
       </c>
       <c r="S18" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="T18" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -17716,10 +17716,10 @@
         <v>47</v>
       </c>
       <c r="S19" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="T19" t="n">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -17792,10 +17792,10 @@
         <v>39</v>
       </c>
       <c r="S20" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="T20" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -17868,10 +17868,10 @@
         <v>34</v>
       </c>
       <c r="S21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T21" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -18892,13 +18892,13 @@
         <v>31</v>
       </c>
       <c r="N2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O2" t="n">
         <v>35</v>
       </c>
       <c r="P2" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -18948,13 +18948,13 @@
         <v>81</v>
       </c>
       <c r="N3" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O3" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P3" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -19010,10 +19010,10 @@
         <v>29</v>
       </c>
       <c r="O4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -19066,13 +19066,13 @@
         <v>32</v>
       </c>
       <c r="N5" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="O5" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="P5" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>79</v>
       </c>
       <c r="P7" t="n">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -19225,13 +19225,13 @@
         <v>36</v>
       </c>
       <c r="N8" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="O8" t="n">
         <v>36</v>
       </c>
       <c r="P8" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -19284,13 +19284,13 @@
         <v>71</v>
       </c>
       <c r="N9" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O9" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="P9" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -19340,13 +19340,13 @@
         <v>22</v>
       </c>
       <c r="N10" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O10" t="n">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="P10" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -19484,13 +19484,13 @@
         <v>11</v>
       </c>
       <c r="N13" t="n">
+        <v>49</v>
+      </c>
+      <c r="O13" t="n">
         <v>23</v>
       </c>
-      <c r="O13" t="n">
-        <v>21</v>
-      </c>
       <c r="P13" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -19543,10 +19543,10 @@
         <v>14</v>
       </c>
       <c r="O14" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="P14" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -19684,13 +19684,13 @@
         <v>69</v>
       </c>
       <c r="N17" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="O17" t="n">
-        <v>138</v>
+        <v>89</v>
       </c>
       <c r="P17" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -19740,13 +19740,13 @@
         <v>94</v>
       </c>
       <c r="N18" t="n">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="O18" t="n">
         <v>51</v>
       </c>
       <c r="P18" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -19796,13 +19796,13 @@
         <v>53</v>
       </c>
       <c r="N19" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P19" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>

--- a/docs/DBS4_Corrections_by_Situation_20260921-dbcd48b8.xlsx
+++ b/docs/DBS4_Corrections_by_Situation_20260921-dbcd48b8.xlsx
@@ -2468,7 +2468,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Push TOS +20% (no click requirement on file → +20% (a stated departure: the logic document would hold at the ceiling)): $7.80 → $9.36; modifier 212%; daily read to 09-28</t>
+          <t>Push TOS +20% (loss stop reached — at 7.80 a top-of-search order already costs 94 (stop 3× contribution = 81)): $7.80 → $7.80; modifier 160%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>Push TOS +30% (30% of required top-of-search clicks delivered → +30%; stopped at the loss stop 12.63): $9.76 → $12.63; modifier 430%; daily read to 09-28</t>
+          <t>Push TOS +30% (30% of required top-of-search clicks delivered → +30%): $9.76 → $12.69; modifier 433%; daily read to 09-28</t>
         </is>
       </c>
     </row>
